--- a/data/Rename_columns.xlsx
+++ b/data/Rename_columns.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D521"/>
+  <dimension ref="A1:D525"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="25.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>centre analytique</t>
+          <t>centre_cout</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1454,10 +1454,8 @@
           <t>Standard</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="D44" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1512,7 +1510,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>centre analytique</t>
+          <t>centre_cout</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1520,10 +1518,8 @@
           <t>Standard</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="D47" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -7966,12 +7962,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>date_operation</t>
+          <t>date_saisie</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Perfect Vision</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D342" t="b">
@@ -8726,7 +8722,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>devise</t>
+          <t>code_devise</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -11555,6 +11551,86 @@
         </is>
       </c>
       <c r="D521" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>code_centre_cout</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>centre_cout</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Perfect Vision</t>
+        </is>
+      </c>
+      <c r="D522" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Numero de la piece d'identite</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Num?ro de la pi?ce d?identit?</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Perfect Vision</t>
+        </is>
+      </c>
+      <c r="D523" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>numero_piece_identite</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Num?ro de la pi?ce d?identit?</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D524" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Mode Desabonne</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Mode D?sabonn?</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D525" t="b">
         <v>0</v>
       </c>
     </row>

--- a/data/Rename_columns.xlsx
+++ b/data/Rename_columns.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D525"/>
+  <dimension ref="A1:D577"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="25.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9322,12 +9322,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>ID_POINT_SERVICE</t>
+          <t>point_service</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Perfect Vision - colonne conservee</t>
+          <t>Perfect Vision</t>
         </is>
       </c>
       <c r="D410" t="b">
@@ -9382,12 +9382,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>ID_TYPE_OPERATION</t>
+          <t>type_operation</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Perfect Vision - colonne conservee</t>
+          <t>Perfect Vision</t>
         </is>
       </c>
       <c r="D413" t="b">
@@ -11632,6 +11632,1054 @@
       </c>
       <c r="D525" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>analyse_source</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>analyse</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D526" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>type_ligne</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>type_element</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D527" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>ligne_excel</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>ligne_reporting</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D528" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>source_donnee</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>origine_donnee</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D529" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>source_declaration</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>origine_declaration</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D530" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>statut_revue_conformite</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>statut_revue</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D531" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>etat_alerte</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>etat</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D532" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>description_alerte</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D533" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>motif_etat</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>motif</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D534" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>reference_operation_perfect</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>numero_operation</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D535" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>id_operation_lab</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>numero_operation</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D536" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>identifiant_liste</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>reference_liste</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D537" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>id_cloture_compte</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>reference_cloture</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D538" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>id_arrete_caisse</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>reference_arrete</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D539" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>id_cycle_tontine</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>reference_cycle</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D540" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>id_depart_adherent</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>reference_depart</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D541" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>JOB_EXECUTION_ID</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>reference_execution</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D542" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>id_mouvement</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>reference_mouvement</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D543" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>analyse</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>analyse</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D544" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>type_element</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>type_element</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D545" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D546" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>ligne_reporting</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>ligne_reporting</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D547" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>rubrique</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>rubrique</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D548" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>date_evenement</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>date_evenement</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D549" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>numero_alerte</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>numero_alerte</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D550" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>reference_interne</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>reference_interne</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D551" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>reference_externe</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>reference_externe</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D552" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>numero_operation</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>numero_operation</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D553" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>etat</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>etat</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D554" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>statut_revue</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>statut_revue</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D555" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>statut_couverture</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>statut_couverture</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D556" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>origine_declaration</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>origine_declaration</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D557" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D558" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D559" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>profil_risque</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>profil_risque</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D560" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>severite</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>severite</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D561" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>action_recommandee</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>action_recommandee</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D562" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>origine_donnee</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>origine_donnee</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D563" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>point_service</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>point_service</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D564" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>motif</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>motif</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D565" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>indicateurs</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>indicateurs</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D566" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>reference_liste</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>reference_liste</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D567" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>reference_cloture</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>reference_cloture</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D568" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>reference_arrete</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>reference_arrete</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D569" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>reference_cycle</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>reference_cycle</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D570" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>reference_depart</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>reference_depart</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D571" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>reference_execution</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>reference_execution</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D572" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>reference_mouvement</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>reference_mouvement</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Conformité</t>
+        </is>
+      </c>
+      <c r="D573" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>reference_ecriture</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>piece_id</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Tous cycles</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>reference_compte</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>compte_id</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Tous cycles</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>numero_operation_annulee</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>id_operation_annulee</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Op?rations</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>numero_operation_origine</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>id_operation_mere</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Op?rations</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/Rename_columns.xlsx
+++ b/data/Rename_columns.xlsx
@@ -3,12 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28800" yWindow="0" windowWidth="14400" windowHeight="15600" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$D$579</definedName>
+  </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -31,19 +33,68 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.7999816888943144"/>
+        <bgColor theme="4" tint="0.7999816888943144"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.5999938962981048"/>
+        <bgColor theme="4" tint="0.5999938962981048"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -54,66 +105,54 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom style="thin">
+      <top style="thin">
         <color auto="1"/>
-      </bottom>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <b val="1"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <condense val="0"/>
-        <color auto="1"/>
-        <extend val="0"/>
-        <sz val="11"/>
-        <vertAlign val="baseline"/>
-      </font>
-      <alignment horizontal="center" vertical="top"/>
-      <border outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -184,22 +223,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tableau1" displayName="Tableau1" ref="A1:D325" headerRowCount="1" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
-  <autoFilter ref="A1:D325"/>
-  <sortState ref="A2:D325">
-    <sortCondition ref="B1:B325"/>
-  </sortState>
-  <tableColumns count="4">
-    <tableColumn id="1" name="Original"/>
-    <tableColumn id="2" name="Renamed"/>
-    <tableColumn id="3" name="Cycle"/>
-    <tableColumn id="4" name="Comparaison"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -491,7144 +514,7144 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D577"/>
+  <dimension ref="A1:D578"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="25.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="21.85546875" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="19.42578125" customWidth="1" min="3" max="3"/>
     <col width="17.140625" bestFit="1" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Renamed</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Cycle</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Comparaison</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>activite client</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>activite_economique</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>activite_economique</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>activite_economique</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>profession</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>activite_economique</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>secteur_activite</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>activite_economique</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>adresse</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>adresse</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>adresse client</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>adresse</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>localisation_client</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>adresse</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>residence</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>adresse</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>age</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>age</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>age client</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>age</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>age du client</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>age</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>agence</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>agence</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>branch</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>agence</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>bureau</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>agence</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>succursale</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>agence</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>agent_credit</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>agent_credit</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>charge_portefeuille</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>agent_credit</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>gestionnaire</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>agent_credit</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>officier_credit</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>agent_credit</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>agent_id</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>agent_id</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D21" t="b">
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>code agent</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>code_agent</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>employee id</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="1" t="inlineStr">
         <is>
           <t>agent_id</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D23" t="b">
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>id agent</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>agent_id</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D24" t="b">
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>matricule agent</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr">
         <is>
           <t>agent_id</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D25" t="b">
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>application</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>application_source</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>application source</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="1" t="inlineStr">
         <is>
           <t>application_source</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>application_source</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>application_source</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>syst?me source</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="1" t="inlineStr">
         <is>
           <t>application_source</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>systeme</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>application_source</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>systeme source</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="1" t="inlineStr">
         <is>
           <t>application_source</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>bank</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>banque</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>banque</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="1" t="inlineStr">
         <is>
           <t>banque</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>institution bancaire</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>banque</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>nom banque</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="1" t="inlineStr">
         <is>
           <t>banque</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>agent caisse</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>caissier</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>caissier</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="1" t="inlineStr">
         <is>
           <t>caissier</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>caissier guichet</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>caissier</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>cashier</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="1" t="inlineStr">
         <is>
           <t>caissier</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>nom caissier</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>caissier</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>categorie</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="1" t="inlineStr">
         <is>
           <t>categorie</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>categorie client</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>categorie</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>centre analytique</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="1" t="inlineStr">
         <is>
           <t>centre analytique</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>centre cout</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>centre_cout</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D44" t="b">
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>centre de co?t</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="1" t="inlineStr">
         <is>
           <t>centre analytique</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>centre de cout</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>centre analytique</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>centre_cout</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="1" t="inlineStr">
         <is>
           <t>centre_cout</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D47" t="b">
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>cost center</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>centre analytique</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>charge_mensuelle</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="1" t="inlineStr">
         <is>
           <t>charge_mensuelle</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>charges</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>charge_mensuelle</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>charges_mensuelles</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="1" t="inlineStr">
         <is>
           <t>charge_mensuelle</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>depenses_mensuelles</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>charge_mensuelle</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="1" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>code_client</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>code_client</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>id_client</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="1" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>num_client</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>num_client</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>numero_client</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="1" t="inlineStr">
         <is>
           <t>numero_client</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>reference_client</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>reference_client</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>commentaire</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="1" t="inlineStr">
         <is>
           <t>commentaire</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>commentaire brut</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>commentaire</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="1" t="inlineStr">
         <is>
           <t>commentaire</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>observation</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>commentaire</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>observations</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="1" t="inlineStr">
         <is>
           <t>commentaire</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>bank account</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>compte_bancaire</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>compte bancaire</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="1" t="inlineStr">
         <is>
           <t>compte_bancaire</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D65" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>compte_bancaire</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>compte_bancaire</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>num compte bancaire</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="1" t="inlineStr">
         <is>
           <t>compte_bancaire</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D67" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="7" t="inlineStr">
         <is>
           <t>numero compte bancaire</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>compte_bancaire</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>compte comptable</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="1" t="inlineStr">
         <is>
           <t>compte_comptable</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D69" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="7" t="inlineStr">
         <is>
           <t>compte gl</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>compte_comptable</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>compte_comptable</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="1" t="inlineStr">
         <is>
           <t>compte_comptable</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D71" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>gl account</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>compte_comptable</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>num compte comptable</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="1" t="inlineStr">
         <is>
           <t>compte_comptable</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D73" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="7" t="inlineStr">
         <is>
           <t>numero compte comptable</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>compte_comptable</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>compte</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="1" t="inlineStr">
         <is>
           <t>compte_id</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D75" t="b">
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D75" s="1" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="7" t="inlineStr">
         <is>
           <t>compte_id</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>compte_id</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>n compte</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="1" t="inlineStr">
         <is>
           <t>num_compte</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D77" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="7" t="inlineStr">
         <is>
           <t>num_compte</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>num_compte</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>numero_compte</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="1" t="inlineStr">
         <is>
           <t>num_compte</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D79" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="7" t="inlineStr">
         <is>
           <t>n° compte</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>num_compte</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>cycle</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="1" t="inlineStr">
         <is>
           <t>cycle_activite</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D81" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>cycle d'activite</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>cycle_activite</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>cycle_activite</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="1" t="inlineStr">
         <is>
           <t>cycle_activite</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D83" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="7" t="inlineStr">
         <is>
           <t>type cycle</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>cycle_activite</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>type de cycle</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="1" t="inlineStr">
         <is>
           <t>cycle_activite</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D85" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="7" t="inlineStr">
         <is>
           <t>activation date</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>date_activation</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>date activation</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="1" t="inlineStr">
         <is>
           <t>date_activation</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D87" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="7" t="inlineStr">
         <is>
           <t>date ouverture acces</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>date_ouverture</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>date_activation</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="1" t="inlineStr">
         <is>
           <t>date_activation</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D89" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="7" t="inlineStr">
         <is>
           <t>date approbation</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>date_decision</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>date_decision</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="1" t="inlineStr">
         <is>
           <t>date_decision</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D91" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="7" t="inlineStr">
         <is>
           <t>date_validation</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>date_decision</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>date dossier</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="1" t="inlineStr">
         <is>
           <t>date_demande</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D93" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="7" t="inlineStr">
         <is>
           <t>date soumission</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>date_demande</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t>date_de_demande</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="1" t="inlineStr">
         <is>
           <t>date_demande</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D95" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="7" t="inlineStr">
         <is>
           <t>date_demande</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>date_demande</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>date d'entree</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="1" t="inlineStr">
         <is>
           <t>date_entree</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D97" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="7" t="inlineStr">
         <is>
           <t>date d?arriv?e</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>date_entree</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>date entree</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="1" t="inlineStr">
         <is>
           <t>date_entree</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D99" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="7" t="inlineStr">
         <is>
           <t>date recrutement</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>date_entree</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>date_entree</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="1" t="inlineStr">
         <is>
           <t>date_entree</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D101" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="7" t="inlineStr">
         <is>
           <t>hiring date</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>date_entree</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>date de l'operation</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="1" t="inlineStr">
         <is>
           <t>date_operation</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D103" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="7" t="inlineStr">
         <is>
           <t>date derniere transaction</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>date_operation</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
+      <c r="C104" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>date_operation</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="1" t="inlineStr">
         <is>
           <t>date_operation</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="7" t="inlineStr">
         <is>
           <t>date_transaction</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>date_operation</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="6" t="inlineStr">
         <is>
           <t>date fermeture acces</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B107" s="1" t="inlineStr">
         <is>
           <t>date_revocation</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D107" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="7" t="inlineStr">
         <is>
           <t>date r?vocation</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>date_revocation</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>date revocation</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B109" s="1" t="inlineStr">
         <is>
           <t>date_revocation</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D109" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="7" t="inlineStr">
         <is>
           <t>date_revocation</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>date_revocation</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>revocation date</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B111" s="1" t="inlineStr">
         <is>
           <t>date_revocation</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D111" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="7" t="inlineStr">
         <is>
           <t>backup date</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B112" s="8" t="inlineStr">
         <is>
           <t>date_sauvegarde</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="6" t="inlineStr">
         <is>
           <t>date backup</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B113" s="1" t="inlineStr">
         <is>
           <t>date_sauvegarde</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D113" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="7" t="inlineStr">
         <is>
           <t>date sauvegarde</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B114" s="8" t="inlineStr">
         <is>
           <t>date_sauvegarde</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
+      <c r="C114" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D114" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="6" t="inlineStr">
         <is>
           <t>date_sauvegarde</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B115" s="1" t="inlineStr">
         <is>
           <t>date_sauvegarde</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D115" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="7" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B116" s="8" t="inlineStr">
         <is>
           <t>devise</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
+      <c r="C116" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="6" t="inlineStr">
         <is>
           <t>devise</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B117" s="1" t="inlineStr">
         <is>
           <t>devise</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D117" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="7" t="inlineStr">
         <is>
           <t>monnaie</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B118" s="8" t="inlineStr">
         <is>
           <t>devise</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
+      <c r="C118" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D118" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="6" t="inlineStr">
         <is>
           <t>dossier_id</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B119" s="1" t="inlineStr">
         <is>
           <t>dossier_id</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D119" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="7" t="inlineStr">
         <is>
           <t>ref_dossier</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B120" s="8" t="inlineStr">
         <is>
           <t>dossier_id</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="6" t="inlineStr">
         <is>
           <t>reference_dossier</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B121" s="1" t="inlineStr">
         <is>
           <t>dossier_id</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D121" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="7" t="inlineStr">
         <is>
           <t>duree</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B122" s="8" t="inlineStr">
         <is>
           <t>duree_credit_mois</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
+      <c r="C122" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D122" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="6" t="inlineStr">
         <is>
           <t>duree_credit</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B123" s="1" t="inlineStr">
         <is>
           <t>duree_credit_mois</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
+      <c r="C123" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D123" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="7" t="inlineStr">
         <is>
           <t>duree_credit_mois</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B124" s="8" t="inlineStr">
         <is>
           <t>duree_credit_mois</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
+      <c r="C124" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D124" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="A125" s="6" t="inlineStr">
         <is>
           <t>duree_mois</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B125" s="1" t="inlineStr">
         <is>
           <t>duree_credit_mois</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D125" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="A126" s="7" t="inlineStr">
         <is>
           <t>nombre_mois</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B126" s="8" t="inlineStr">
         <is>
           <t>duree_credit_mois</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
+      <c r="C126" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D126" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="6" t="inlineStr">
         <is>
           <t>?cart caisse</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B127" s="1" t="inlineStr">
         <is>
           <t>ecart_caisse</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D127" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="7" t="inlineStr">
         <is>
           <t>diff caisse</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B128" s="8" t="inlineStr">
         <is>
           <t>ecart_caisse</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
+      <c r="C128" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D128" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="A129" s="6" t="inlineStr">
         <is>
           <t>difference caisse</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B129" s="1" t="inlineStr">
         <is>
           <t>ecart_caisse</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D129" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="7" t="inlineStr">
         <is>
           <t>ecart caisse</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B130" s="8" t="inlineStr">
         <is>
           <t>ecart_caisse</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
+      <c r="C130" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D130" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="6" t="inlineStr">
         <is>
           <t>ecart_caisse</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B131" s="1" t="inlineStr">
         <is>
           <t>ecart_caisse</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D131" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="A132" s="7" t="inlineStr">
         <is>
           <t>?cart rapprochement</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B132" s="8" t="inlineStr">
         <is>
           <t>ecart_rapprochement</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
+      <c r="C132" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D132" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="A133" s="6" t="inlineStr">
         <is>
           <t>difference rapprochement</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B133" s="1" t="inlineStr">
         <is>
           <t>ecart_rapprochement</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
+      <c r="C133" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D133" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
+      <c r="A134" s="7" t="inlineStr">
         <is>
           <t>ecart rapprochement</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B134" s="8" t="inlineStr">
         <is>
           <t>ecart_rapprochement</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
+      <c r="C134" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D134" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
+      <c r="A135" s="6" t="inlineStr">
         <is>
           <t>ecart_rapprochement</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B135" s="1" t="inlineStr">
         <is>
           <t>ecart_rapprochement</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
+      <c r="C135" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D135" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
+      <c r="A136" s="7" t="inlineStr">
         <is>
           <t>suspens bancaire</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B136" s="8" t="inlineStr">
         <is>
           <t>ecart_rapprochement</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
+      <c r="C136" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D136" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
+      <c r="A137" s="6" t="inlineStr">
         <is>
           <t>encaisse cl?ture</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B137" s="1" t="inlineStr">
         <is>
           <t>encaisse_fin_jour</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
+      <c r="C137" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D137" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
+      <c r="A138" s="7" t="inlineStr">
         <is>
           <t>encaisse cloture</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B138" s="8" t="inlineStr">
         <is>
           <t>encaisse_fin_jour</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
+      <c r="C138" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D138" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
+      <c r="A139" s="6" t="inlineStr">
         <is>
           <t>encaisse fin jour</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B139" s="1" t="inlineStr">
         <is>
           <t>encaisse_fin_jour</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
+      <c r="C139" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D139" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
+      <c r="A140" s="7" t="inlineStr">
         <is>
           <t>encaisse finale</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B140" s="8" t="inlineStr">
         <is>
           <t>encaisse_fin_jour</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
+      <c r="C140" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D140" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
+      <c r="A141" s="6" t="inlineStr">
         <is>
           <t>encaisse_fin_jour</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B141" s="1" t="inlineStr">
         <is>
           <t>encaisse_fin_jour</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
+      <c r="C141" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D141" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="A142" s="7" t="inlineStr">
         <is>
           <t>solde caisse fin jour</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B142" s="8" t="inlineStr">
         <is>
           <t>encaisse_fin_jour</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
+      <c r="C142" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D142" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="A143" s="6" t="inlineStr">
         <is>
           <t>fonction</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B143" s="1" t="inlineStr">
         <is>
           <t>fonction</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
+      <c r="C143" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D143" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="A144" s="7" t="inlineStr">
         <is>
           <t>job title</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B144" s="8" t="inlineStr">
         <is>
           <t>fonction</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
+      <c r="C144" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D144" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
+      <c r="A145" s="6" t="inlineStr">
         <is>
           <t>poste</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="B145" s="1" t="inlineStr">
         <is>
           <t>fonction</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
+      <c r="C145" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D145" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
+      <c r="A146" s="7" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
+      <c r="B146" s="8" t="inlineStr">
         <is>
           <t>fonction</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
+      <c r="C146" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D146" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
+      <c r="A147" s="6" t="inlineStr">
         <is>
           <t>garantie</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="B147" s="1" t="inlineStr">
         <is>
           <t>garantie</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
+      <c r="C147" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D147" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
+      <c r="A148" s="7" t="inlineStr">
         <is>
           <t>garanties</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="B148" s="8" t="inlineStr">
         <is>
           <t>garantie</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
+      <c r="C148" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D148" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
+      <c r="A149" s="6" t="inlineStr">
         <is>
           <t>surete</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="B149" s="1" t="inlineStr">
         <is>
           <t>garantie</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
+      <c r="C149" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D149" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
+      <c r="A150" s="7" t="inlineStr">
         <is>
           <t>type_garantie</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="B150" s="8" t="inlineStr">
         <is>
           <t>garantie</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
+      <c r="C150" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D150" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
+      <c r="A151" s="6" t="inlineStr">
         <is>
           <t>id_dossier</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B151" s="1" t="inlineStr">
         <is>
           <t>id_dossier</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
+      <c r="C151" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D151" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
+      <c r="A152" s="7" t="inlineStr">
         <is>
           <t>asset id</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="B152" s="8" t="inlineStr">
         <is>
           <t>immobilisation_id</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
+      <c r="C152" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D152" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
+      <c r="A153" s="6" t="inlineStr">
         <is>
           <t>code immobilisation</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="B153" s="1" t="inlineStr">
         <is>
           <t>immobilisation_id</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
+      <c r="C153" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D153" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
+      <c r="A154" s="7" t="inlineStr">
         <is>
           <t>immobilisation id</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B154" s="8" t="inlineStr">
         <is>
           <t>immobilisation_id</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
+      <c r="C154" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D154" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
+      <c r="A155" s="6" t="inlineStr">
         <is>
           <t>immobilisation_id</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B155" s="1" t="inlineStr">
         <is>
           <t>immobilisation_id</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
+      <c r="C155" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D155" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
+      <c r="A156" s="7" t="inlineStr">
         <is>
           <t>numero immobilisation</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B156" s="8" t="inlineStr">
         <is>
           <t>immobilisation_id</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
+      <c r="C156" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D156" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
+      <c r="A157" s="6" t="inlineStr">
         <is>
           <t>incident critique</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B157" s="1" t="inlineStr">
         <is>
           <t>incident_majeur</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
+      <c r="C157" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D157" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
+      <c r="A158" s="7" t="inlineStr">
         <is>
           <t>incident majeur</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B158" s="8" t="inlineStr">
         <is>
           <t>incident_majeur</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
+      <c r="C158" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D158" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
+      <c r="A159" s="6" t="inlineStr">
         <is>
           <t>incident_majeur</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B159" s="1" t="inlineStr">
         <is>
           <t>incident_majeur</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
+      <c r="C159" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D159" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
+      <c r="A160" s="7" t="inlineStr">
         <is>
           <t>panne majeure</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="B160" s="8" t="inlineStr">
         <is>
           <t>incident_majeur</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
+      <c r="C160" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D160" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
+      <c r="A161" s="6" t="inlineStr">
         <is>
           <t>sinistre majeur</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
+      <c r="B161" s="1" t="inlineStr">
         <is>
           <t>incident_majeur</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
+      <c r="C161" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D161" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
+      <c r="A162" s="7" t="inlineStr">
         <is>
           <t>code journal</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
+      <c r="B162" s="8" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
+      <c r="C162" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D162" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
+      <c r="A163" s="6" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="B163" s="1" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
+      <c r="C163" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D163" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
+      <c r="A164" s="7" t="inlineStr">
         <is>
           <t>journal comptable</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="B164" s="8" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
+      <c r="C164" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D164" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
+      <c r="A165" s="6" t="inlineStr">
         <is>
           <t>libelle journal</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="B165" s="1" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
+      <c r="C165" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D165" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
+      <c r="A166" s="7" t="inlineStr">
         <is>
           <t>journal des transactions</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
+      <c r="B166" s="8" t="inlineStr">
         <is>
           <t>journal_transaction</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
+      <c r="C166" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D166" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
+      <c r="A167" s="6" t="inlineStr">
         <is>
           <t>journal_transaction</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
+      <c r="B167" s="1" t="inlineStr">
         <is>
           <t>journal_transaction</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
+      <c r="C167" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D167" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
+      <c r="A168" s="7" t="inlineStr">
         <is>
           <t>registre_transaction</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
+      <c r="B168" s="8" t="inlineStr">
         <is>
           <t>journal_transaction</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
+      <c r="C168" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D168" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
+      <c r="A169" s="6" t="inlineStr">
         <is>
           <t>n° manuel</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
+      <c r="B169" s="1" t="inlineStr">
         <is>
           <t>manuel_id</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
+      <c r="C169" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D169" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
+      <c r="A170" s="7" t="inlineStr">
         <is>
           <t>N° manuel</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="B170" s="8" t="inlineStr">
         <is>
           <t>manuel_id</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
+      <c r="C170" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D170" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
+      <c r="A171" s="6" t="inlineStr">
         <is>
           <t>montant credit accorde</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="B171" s="1" t="inlineStr">
         <is>
           <t>montant_accorde</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
+      <c r="C171" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D171" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
+      <c r="A172" s="7" t="inlineStr">
         <is>
           <t>montant decaisse</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B172" s="8" t="inlineStr">
         <is>
           <t>montant_accorde</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
+      <c r="C172" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D172" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
+      <c r="A173" s="6" t="inlineStr">
         <is>
           <t>montant valide</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="B173" s="1" t="inlineStr">
         <is>
           <t>montant_accorde</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
+      <c r="C173" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D173" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
+      <c r="A174" s="7" t="inlineStr">
         <is>
           <t>montant_accorde</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B174" s="8" t="inlineStr">
         <is>
           <t>montant_accorde</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
+      <c r="C174" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D174" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
+      <c r="A175" s="6" t="inlineStr">
         <is>
           <t>cr?dit</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B175" s="1" t="inlineStr">
         <is>
           <t>montant_credit</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
+      <c r="C175" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D175" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
+      <c r="A176" s="7" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B176" s="8" t="inlineStr">
         <is>
           <t>montant_credit</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
+      <c r="C176" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D176" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
+      <c r="A177" s="6" t="inlineStr">
         <is>
           <t>montant au cr?dit</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B177" s="1" t="inlineStr">
         <is>
           <t>montant_credit</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
+      <c r="C177" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D177" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
+      <c r="A178" s="7" t="inlineStr">
         <is>
           <t>montant au credit</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="B178" s="8" t="inlineStr">
         <is>
           <t>montant_credit</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
+      <c r="C178" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D178" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
+      <c r="A179" s="6" t="inlineStr">
         <is>
           <t>montant credit</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="B179" s="1" t="inlineStr">
         <is>
           <t>montant_credit</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
+      <c r="C179" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D179" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
+      <c r="A180" s="7" t="inlineStr">
         <is>
           <t>montant_credit</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="B180" s="8" t="inlineStr">
         <is>
           <t>montant_credit</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
+      <c r="C180" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D180" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
+      <c r="A181" s="6" t="inlineStr">
         <is>
           <t>d?bit</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B181" s="1" t="inlineStr">
         <is>
           <t>montant_debit</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
+      <c r="C181" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D181" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
+      <c r="A182" s="7" t="inlineStr">
         <is>
           <t>debit</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B182" s="8" t="inlineStr">
         <is>
           <t>montant_debit</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
+      <c r="C182" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D182" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
+      <c r="A183" s="6" t="inlineStr">
         <is>
           <t>montant au d?bit</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B183" s="1" t="inlineStr">
         <is>
           <t>montant_debit</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
+      <c r="C183" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D183" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
+      <c r="A184" s="7" t="inlineStr">
         <is>
           <t>montant au debit</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="B184" s="8" t="inlineStr">
         <is>
           <t>montant_debit</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
+      <c r="C184" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D184" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
+      <c r="A185" s="6" t="inlineStr">
         <is>
           <t>montant debit</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B185" s="1" t="inlineStr">
         <is>
           <t>montant_debit</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
+      <c r="C185" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D185" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
+      <c r="A186" s="7" t="inlineStr">
         <is>
           <t>montant_debit</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B186" s="8" t="inlineStr">
         <is>
           <t>montant_debit</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
+      <c r="C186" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D186" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
+      <c r="A187" s="6" t="inlineStr">
         <is>
           <t>montant credit demande</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
+      <c r="B187" s="1" t="inlineStr">
         <is>
           <t>montant_demande</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
+      <c r="C187" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D187" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
+      <c r="A188" s="7" t="inlineStr">
         <is>
           <t>montant sollicite</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
+      <c r="B188" s="8" t="inlineStr">
         <is>
           <t>montant_demande</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
+      <c r="C188" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D188" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
+      <c r="A189" s="6" t="inlineStr">
         <is>
           <t>montant_demande</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
+      <c r="B189" s="1" t="inlineStr">
         <is>
           <t>montant_demande</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
+      <c r="C189" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D189" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
+      <c r="A190" s="7" t="inlineStr">
         <is>
           <t>montant_solicite</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
+      <c r="B190" s="8" t="inlineStr">
         <is>
           <t>montant_demande</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
+      <c r="C190" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D190" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
+      <c r="A191" s="6" t="inlineStr">
         <is>
           <t>montant_operation</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
+      <c r="B191" s="1" t="inlineStr">
         <is>
           <t>montant_operation</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
+      <c r="C191" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D191" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
+      <c r="A192" s="7" t="inlineStr">
         <is>
           <t>montant_transaction</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="B192" s="8" t="inlineStr">
         <is>
           <t>montant_operation</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
+      <c r="C192" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D192" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
+      <c r="A193" s="6" t="inlineStr">
         <is>
           <t>nb epg</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="B193" s="1" t="inlineStr">
         <is>
           <t>nbre_epg</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
+      <c r="C193" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D193" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
+      <c r="A194" s="7" t="inlineStr">
         <is>
           <t>Nb epg</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
+      <c r="B194" s="8" t="inlineStr">
         <is>
           <t>nbre_epg</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
+      <c r="C194" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D194" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
+      <c r="A195" s="6" t="inlineStr">
         <is>
           <t>access level</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
+      <c r="B195" s="1" t="inlineStr">
         <is>
           <t>niveau_habilitation</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
+      <c r="C195" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D195" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
+      <c r="A196" s="7" t="inlineStr">
         <is>
           <t>niveau d'habilitation</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
+      <c r="B196" s="8" t="inlineStr">
         <is>
           <t>niveau_habilitation</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
+      <c r="C196" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D196" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
+      <c r="A197" s="6" t="inlineStr">
         <is>
           <t>niveau d?habilitation</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
+      <c r="B197" s="1" t="inlineStr">
         <is>
           <t>niveau_habilitation</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
+      <c r="C197" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D197" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
+      <c r="A198" s="7" t="inlineStr">
         <is>
           <t>niveau habilitation</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
+      <c r="B198" s="8" t="inlineStr">
         <is>
           <t>niveau_habilitation</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
+      <c r="C198" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D198" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
+      <c r="A199" s="6" t="inlineStr">
         <is>
           <t>niveau_habilitation</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="B199" s="1" t="inlineStr">
         <is>
           <t>niveau_habilitation</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
+      <c r="C199" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D199" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr">
+      <c r="A200" s="7" t="inlineStr">
         <is>
           <t>classe_risque</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
+      <c r="B200" s="8" t="inlineStr">
         <is>
           <t>niveau_risque</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
+      <c r="C200" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D200" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
+      <c r="A201" s="6" t="inlineStr">
         <is>
           <t>niveau_risque</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
+      <c r="B201" s="1" t="inlineStr">
         <is>
           <t>niveau_risque</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
+      <c r="C201" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D201" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
+      <c r="A202" s="7" t="inlineStr">
         <is>
           <t>risque</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
+      <c r="B202" s="8" t="inlineStr">
         <is>
           <t>niveau_risque</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
+      <c r="C202" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D202" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
+      <c r="A203" s="6" t="inlineStr">
         <is>
           <t>client</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
+      <c r="B203" s="1" t="inlineStr">
         <is>
           <t>nom_client</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
+      <c r="C203" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D203" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
+      <c r="A204" s="7" t="inlineStr">
         <is>
           <t>full_name</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
+      <c r="B204" s="8" t="inlineStr">
         <is>
           <t>nom_client</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
+      <c r="C204" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D204" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
+      <c r="A205" s="6" t="inlineStr">
         <is>
           <t>nom</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
+      <c r="B205" s="1" t="inlineStr">
         <is>
           <t>nom_client</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
+      <c r="C205" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D205" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
+      <c r="A206" s="7" t="inlineStr">
         <is>
           <t>nom_client</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="B206" s="8" t="inlineStr">
         <is>
           <t>nom_client</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
+      <c r="C206" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D206" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
+      <c r="A207" s="6" t="inlineStr">
         <is>
           <t>nom_complet</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B207" s="1" t="inlineStr">
         <is>
           <t>nom_client</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
+      <c r="C207" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D207" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr">
+      <c r="A208" s="7" t="inlineStr">
         <is>
           <t>groupe</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B208" s="8" t="inlineStr">
         <is>
           <t>nom_groupe</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
+      <c r="C208" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D208" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
+      <c r="A209" s="6" t="inlineStr">
         <is>
           <t>groupe solidaire</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B209" s="1" t="inlineStr">
         <is>
           <t>nom_groupe</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
+      <c r="C209" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D209" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr">
+      <c r="A210" s="7" t="inlineStr">
         <is>
           <t>nom du groupe</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="B210" s="8" t="inlineStr">
         <is>
           <t>nom_groupe</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
+      <c r="C210" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D210" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr">
+      <c r="A211" s="6" t="inlineStr">
         <is>
           <t>nom_groupe</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="B211" s="1" t="inlineStr">
         <is>
           <t>nom_groupe</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
+      <c r="C211" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D211" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr">
+      <c r="A212" s="7" t="inlineStr">
         <is>
           <t>num_dossier</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="B212" s="8" t="inlineStr">
         <is>
           <t>dossier_id</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr">
+      <c r="C212" s="8" t="inlineStr">
         <is>
           <t>Perfect Vision</t>
         </is>
       </c>
-      <c r="D212" t="b">
+      <c r="D212" s="8" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr">
+      <c r="A213" s="6" t="inlineStr">
         <is>
           <t>numero_dossier</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B213" s="1" t="inlineStr">
         <is>
           <t>num_dossier</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
+      <c r="C213" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D213" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr">
+      <c r="A214" s="7" t="inlineStr">
         <is>
           <t>num_reference</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
+      <c r="B214" s="8" t="inlineStr">
         <is>
           <t>numero_reference</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
+      <c r="C214" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D214" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
+      <c r="A215" s="6" t="inlineStr">
         <is>
           <t>numero de reference</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
+      <c r="B215" s="1" t="inlineStr">
         <is>
           <t>numero_reference</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
+      <c r="C215" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D215" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
+      <c r="A216" s="7" t="inlineStr">
         <is>
           <t>numero_reference</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
+      <c r="B216" s="8" t="inlineStr">
         <is>
           <t>numero_reference</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
+      <c r="C216" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D216" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
+      <c r="A217" s="6" t="inlineStr">
         <is>
           <t>reference</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
+      <c r="B217" s="1" t="inlineStr">
         <is>
           <t>numero_reference</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
+      <c r="C217" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D217" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
+      <c r="A218" s="7" t="inlineStr">
         <is>
           <t>reference_transaction</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="B218" s="8" t="inlineStr">
         <is>
           <t>numero_reference</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
+      <c r="C218" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D218" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
+      <c r="A219" s="6" t="inlineStr">
         <is>
           <t>agent operateur</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B219" s="1" t="inlineStr">
         <is>
           <t>operateur</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
+      <c r="C219" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D219" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr">
+      <c r="A220" s="7" t="inlineStr">
         <is>
           <t>operateur</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="B220" s="8" t="inlineStr">
         <is>
           <t>operateur</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
+      <c r="C220" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D220" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr">
+      <c r="A221" s="6" t="inlineStr">
         <is>
           <t>operateur money provider</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B221" s="1" t="inlineStr">
         <is>
           <t>operateur</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
+      <c r="C221" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D221" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr">
+      <c r="A222" s="7" t="inlineStr">
         <is>
           <t>id piece</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B222" s="8" t="inlineStr">
         <is>
           <t>piece_id</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
+      <c r="C222" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D222" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr">
+      <c r="A223" s="6" t="inlineStr">
         <is>
           <t>num piece</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B223" s="1" t="inlineStr">
         <is>
           <t>piece_id</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
+      <c r="C223" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D223" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr">
+      <c r="A224" s="7" t="inlineStr">
         <is>
           <t>numero piece</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
+      <c r="B224" s="8" t="inlineStr">
         <is>
           <t>piece_id</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
+      <c r="C224" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D224" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr">
+      <c r="A225" s="6" t="inlineStr">
         <is>
           <t>piece comptable</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
+      <c r="B225" s="1" t="inlineStr">
         <is>
           <t>piece_id</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
+      <c r="C225" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D225" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr">
+      <c r="A226" s="7" t="inlineStr">
         <is>
           <t>piece_id</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
+      <c r="B226" s="8" t="inlineStr">
         <is>
           <t>piece_id</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
+      <c r="C226" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D226" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr">
+      <c r="A227" s="6" t="inlineStr">
         <is>
           <t>reference piece</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="B227" s="1" t="inlineStr">
         <is>
           <t>piece_id</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
+      <c r="C227" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D227" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr">
+      <c r="A228" s="7" t="inlineStr">
         <is>
           <t>access profile</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
+      <c r="B228" s="8" t="inlineStr">
         <is>
           <t>profil_acces</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
+      <c r="C228" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D228" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr">
+      <c r="A229" s="6" t="inlineStr">
         <is>
           <t>profil acces</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
+      <c r="B229" s="1" t="inlineStr">
         <is>
           <t>profil_acces</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
+      <c r="C229" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D229" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr">
+      <c r="A230" s="7" t="inlineStr">
         <is>
           <t>profil d'acces</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
+      <c r="B230" s="8" t="inlineStr">
         <is>
           <t>profil_acces</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
+      <c r="C230" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D230" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr">
+      <c r="A231" s="6" t="inlineStr">
         <is>
           <t>profil d?acc?s</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
+      <c r="B231" s="1" t="inlineStr">
         <is>
           <t>profil_acces</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
+      <c r="C231" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D231" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr">
+      <c r="A232" s="7" t="inlineStr">
         <is>
           <t>profil_acces</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
+      <c r="B232" s="8" t="inlineStr">
         <is>
           <t>profil_acces</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
+      <c r="C232" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D232" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr">
+      <c r="A233" s="6" t="inlineStr">
         <is>
           <t>role acces</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
+      <c r="B233" s="1" t="inlineStr">
         <is>
           <t>profil_acces</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
+      <c r="C233" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D233" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr">
+      <c r="A234" s="7" t="inlineStr">
         <is>
           <t>days_past_due</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
+      <c r="B234" s="8" t="inlineStr">
         <is>
           <t>retard_jours</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
+      <c r="C234" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D234" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
+      <c r="A235" s="6" t="inlineStr">
         <is>
           <t>jours_retard</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B235" s="1" t="inlineStr">
         <is>
           <t>retard_jours</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
+      <c r="C235" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D235" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr">
+      <c r="A236" s="7" t="inlineStr">
         <is>
           <t>nombre_jours_retard</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
+      <c r="B236" s="8" t="inlineStr">
         <is>
           <t>retard_jours</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
+      <c r="C236" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D236" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr">
+      <c r="A237" s="6" t="inlineStr">
         <is>
           <t>retard</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
+      <c r="B237" s="1" t="inlineStr">
         <is>
           <t>retard_jours</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
+      <c r="C237" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D237" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr">
+      <c r="A238" s="7" t="inlineStr">
         <is>
           <t>retard_jours</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
+      <c r="B238" s="8" t="inlineStr">
         <is>
           <t>retard_jours</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
+      <c r="C238" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D238" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
+      <c r="A239" s="6" t="inlineStr">
         <is>
           <t>chiffre_affaire_mensuel</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
+      <c r="B239" s="1" t="inlineStr">
         <is>
           <t>revenu_mensuel</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
+      <c r="C239" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D239" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr">
+      <c r="A240" s="7" t="inlineStr">
         <is>
           <t>revenu</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
+      <c r="B240" s="8" t="inlineStr">
         <is>
           <t>revenu_mensuel</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
+      <c r="C240" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D240" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
+      <c r="A241" s="6" t="inlineStr">
         <is>
           <t>revenu_mensuel</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
+      <c r="B241" s="1" t="inlineStr">
         <is>
           <t>revenu_mensuel</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
+      <c r="C241" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D241" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
+      <c r="A242" s="7" t="inlineStr">
         <is>
           <t>revenus_mensuels</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
+      <c r="B242" s="8" t="inlineStr">
         <is>
           <t>revenu_mensuel</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
+      <c r="C242" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D242" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
+      <c r="A243" s="6" t="inlineStr">
         <is>
           <t>salaire</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
+      <c r="B243" s="1" t="inlineStr">
         <is>
           <t>salaire</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
+      <c r="C243" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D243" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
+      <c r="A244" s="7" t="inlineStr">
         <is>
           <t>paie</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
+      <c r="B244" s="8" t="inlineStr">
         <is>
           <t>salaire</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
+      <c r="C244" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D244" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
+      <c r="A245" s="6" t="inlineStr">
         <is>
           <t>r?mun?ration</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
+      <c r="B245" s="1" t="inlineStr">
         <is>
           <t>salaire</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
+      <c r="C245" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D245" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr">
+      <c r="A246" s="7" t="inlineStr">
         <is>
           <t>remuneration</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
+      <c r="B246" s="8" t="inlineStr">
         <is>
           <t>salaire</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
+      <c r="C246" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D246" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr">
+      <c r="A247" s="6" t="inlineStr">
         <is>
           <t>salaire</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
+      <c r="B247" s="1" t="inlineStr">
         <is>
           <t>salaire</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
+      <c r="C247" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D247" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
+      <c r="A248" s="7" t="inlineStr">
         <is>
           <t>salaire mensuel</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
+      <c r="B248" s="8" t="inlineStr">
         <is>
           <t>salaire</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
+      <c r="C248" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D248" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
+      <c r="A249" s="6" t="inlineStr">
         <is>
           <t>credit_score</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
+      <c r="B249" s="1" t="inlineStr">
         <is>
           <t>score_credit</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
+      <c r="C249" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D249" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
+      <c r="A250" s="7" t="inlineStr">
         <is>
           <t>notation</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
+      <c r="B250" s="8" t="inlineStr">
         <is>
           <t>score_credit</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
+      <c r="C250" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D250" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
+      <c r="A251" s="6" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
+      <c r="B251" s="1" t="inlineStr">
         <is>
           <t>score_credit</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
+      <c r="C251" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D251" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
+      <c r="A252" s="7" t="inlineStr">
         <is>
           <t>score_credit</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
+      <c r="B252" s="8" t="inlineStr">
         <is>
           <t>score_credit</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
+      <c r="C252" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D252" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
+      <c r="A253" s="6" t="inlineStr">
         <is>
           <t>gender</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
+      <c r="B253" s="1" t="inlineStr">
         <is>
           <t>sexe</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
+      <c r="C253" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D253" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
+      <c r="A254" s="7" t="inlineStr">
         <is>
           <t>genre</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
+      <c r="B254" s="8" t="inlineStr">
         <is>
           <t>sexe</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
+      <c r="C254" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D254" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr">
+      <c r="A255" s="6" t="inlineStr">
         <is>
           <t>sex</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
+      <c r="B255" s="1" t="inlineStr">
         <is>
           <t>sexe</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
+      <c r="C255" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D255" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr">
+      <c r="A256" s="7" t="inlineStr">
         <is>
           <t>sexe</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
+      <c r="B256" s="8" t="inlineStr">
         <is>
           <t>sexe</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
+      <c r="C256" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D256" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr">
+      <c r="A257" s="6" t="inlineStr">
         <is>
           <t>sexe client</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B257" s="1" t="inlineStr">
         <is>
           <t>sexe</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
+      <c r="C257" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D257" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr">
+      <c r="A258" s="7" t="inlineStr">
         <is>
           <t>bank balance</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
+      <c r="B258" s="8" t="inlineStr">
         <is>
           <t>solde_banque</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
+      <c r="C258" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D258" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr">
+      <c r="A259" s="6" t="inlineStr">
         <is>
           <t>solde banque</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
+      <c r="B259" s="1" t="inlineStr">
         <is>
           <t>solde_banque</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
+      <c r="C259" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D259" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr">
+      <c r="A260" s="7" t="inlineStr">
         <is>
           <t>solde compte bancaire</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
+      <c r="B260" s="8" t="inlineStr">
         <is>
           <t>solde_banque</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
+      <c r="C260" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D260" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr">
+      <c r="A261" s="6" t="inlineStr">
         <is>
           <t>solde_banque</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
+      <c r="B261" s="1" t="inlineStr">
         <is>
           <t>solde_banque</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
+      <c r="C261" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D261" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr">
+      <c r="A262" s="7" t="inlineStr">
         <is>
           <t>encours</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B262" s="8" t="inlineStr">
         <is>
           <t>solde_compte</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
+      <c r="C262" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D262" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr">
+      <c r="A263" s="6" t="inlineStr">
         <is>
           <t>encours epargnant</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
+      <c r="B263" s="1" t="inlineStr">
         <is>
           <t>solde_compte</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
+      <c r="C263" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D263" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr">
+      <c r="A264" s="7" t="inlineStr">
         <is>
           <t>solde epargne</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
+      <c r="B264" s="8" t="inlineStr">
         <is>
           <t>solde_compte</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
+      <c r="C264" s="8" t="inlineStr">
         <is>
           <t>Perfect Vision</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr">
+      <c r="D264" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr">
+      <c r="A265" s="6" t="inlineStr">
         <is>
           <t>solde_compte</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr">
+      <c r="B265" s="1" t="inlineStr">
         <is>
           <t>solde_compte</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
+      <c r="C265" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D265" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="inlineStr">
+      <c r="A266" s="7" t="inlineStr">
         <is>
           <t>solde cloture</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr">
+      <c r="B266" s="8" t="inlineStr">
         <is>
           <t>solde_final</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
+      <c r="C266" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D266" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="inlineStr">
+      <c r="A267" s="6" t="inlineStr">
         <is>
           <t>solde_final</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
+      <c r="B267" s="1" t="inlineStr">
         <is>
           <t>solde_final</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
+      <c r="C267" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D267" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" t="inlineStr">
+      <c r="A268" s="7" t="inlineStr">
         <is>
           <t>solde debut</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
+      <c r="B268" s="8" t="inlineStr">
         <is>
           <t>solde_initial</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
+      <c r="C268" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D268" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" t="inlineStr">
+      <c r="A269" s="6" t="inlineStr">
         <is>
           <t>solde_initial</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
+      <c r="B269" s="1" t="inlineStr">
         <is>
           <t>solde_initial</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
+      <c r="C269" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D269" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" t="inlineStr">
+      <c r="A270" s="7" t="inlineStr">
         <is>
           <t>?tat agent</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
+      <c r="B270" s="8" t="inlineStr">
         <is>
           <t>statut_agent</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
+      <c r="C270" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D270" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" t="inlineStr">
+      <c r="A271" s="6" t="inlineStr">
         <is>
           <t>etat agent</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr">
+      <c r="B271" s="1" t="inlineStr">
         <is>
           <t>statut_agent</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
+      <c r="C271" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D271" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="272">
-      <c r="A272" t="inlineStr">
+      <c r="A272" s="7" t="inlineStr">
         <is>
           <t>status agent</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
+      <c r="B272" s="8" t="inlineStr">
         <is>
           <t>statut_agent</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
+      <c r="C272" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D272" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="A273" t="inlineStr">
+      <c r="A273" s="6" t="inlineStr">
         <is>
           <t>statut agent</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
+      <c r="B273" s="1" t="inlineStr">
         <is>
           <t>statut_agent</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
+      <c r="C273" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D273" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="inlineStr">
+      <c r="A274" s="7" t="inlineStr">
         <is>
           <t>statut_agent</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
+      <c r="B274" s="8" t="inlineStr">
         <is>
           <t>statut_agent</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
+      <c r="C274" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D274" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="inlineStr">
+      <c r="A275" s="6" t="inlineStr">
         <is>
           <t>etat compte</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
+      <c r="B275" s="1" t="inlineStr">
         <is>
           <t>statut_compte</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
+      <c r="C275" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D275" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr">
+      <c r="A276" s="7" t="inlineStr">
         <is>
           <t>status compte</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
+      <c r="B276" s="8" t="inlineStr">
         <is>
           <t>statut_compte</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
+      <c r="C276" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D276" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" t="inlineStr">
+      <c r="A277" s="6" t="inlineStr">
         <is>
           <t>statut_compte</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
+      <c r="B277" s="1" t="inlineStr">
         <is>
           <t>statut_compte</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
+      <c r="C277" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D277" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" t="inlineStr">
+      <c r="A278" s="7" t="inlineStr">
         <is>
           <t>decision</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
+      <c r="B278" s="8" t="inlineStr">
         <is>
           <t>statut_dossier</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
+      <c r="C278" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D278" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="A279" t="inlineStr">
+      <c r="A279" s="6" t="inlineStr">
         <is>
           <t>etat_dossier</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
+      <c r="B279" s="1" t="inlineStr">
         <is>
           <t>statut_dossier</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
+      <c r="C279" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D279" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="280">
-      <c r="A280" t="inlineStr">
+      <c r="A280" s="7" t="inlineStr">
         <is>
           <t>status_dossier</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr">
+      <c r="B280" s="8" t="inlineStr">
         <is>
           <t>statut_dossier</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
+      <c r="C280" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D280" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="inlineStr">
+      <c r="A281" s="6" t="inlineStr">
         <is>
           <t>statut_dossier</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
+      <c r="B281" s="1" t="inlineStr">
         <is>
           <t>statut_dossier</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
+      <c r="C281" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D281" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="282">
-      <c r="A282" t="inlineStr">
+      <c r="A282" s="7" t="inlineStr">
         <is>
           <t>etat_paiement</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr">
+      <c r="B282" s="8" t="inlineStr">
         <is>
           <t>statut_remboursement</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
+      <c r="C282" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D282" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="A283" t="inlineStr">
+      <c r="A283" s="6" t="inlineStr">
         <is>
           <t>etat_remboursement</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
+      <c r="B283" s="1" t="inlineStr">
         <is>
           <t>statut_remboursement</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
+      <c r="C283" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D283" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="inlineStr">
+      <c r="A284" s="7" t="inlineStr">
         <is>
           <t>status_remboursement</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr">
+      <c r="B284" s="8" t="inlineStr">
         <is>
           <t>statut_remboursement</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
+      <c r="C284" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D284" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="inlineStr">
+      <c r="A285" s="6" t="inlineStr">
         <is>
           <t>statut_remboursement</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr">
+      <c r="B285" s="1" t="inlineStr">
         <is>
           <t>statut_remboursement</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
+      <c r="C285" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D285" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="inlineStr">
+      <c r="A286" s="7" t="inlineStr">
         <is>
           <t>statut du test de reprise</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr">
+      <c r="B286" s="8" t="inlineStr">
         <is>
           <t>statut_test_reprise</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
+      <c r="C286" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D286" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="inlineStr">
+      <c r="A287" s="6" t="inlineStr">
         <is>
           <t>statut restauration</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr">
+      <c r="B287" s="1" t="inlineStr">
         <is>
           <t>statut_test_reprise</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
+      <c r="C287" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D287" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="288">
-      <c r="A288" t="inlineStr">
+      <c r="A288" s="7" t="inlineStr">
         <is>
           <t>statut test reprise</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr">
+      <c r="B288" s="8" t="inlineStr">
         <is>
           <t>statut_test_reprise</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
+      <c r="C288" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D288" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="289">
-      <c r="A289" t="inlineStr">
+      <c r="A289" s="6" t="inlineStr">
         <is>
           <t>statut_test_reprise</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr">
+      <c r="B289" s="1" t="inlineStr">
         <is>
           <t>statut_test_reprise</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
+      <c r="C289" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D289" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="inlineStr">
+      <c r="A290" s="7" t="inlineStr">
         <is>
           <t>test de reprise</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr">
+      <c r="B290" s="8" t="inlineStr">
         <is>
           <t>statut_test_reprise</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
+      <c r="C290" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D290" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="291">
-      <c r="A291" t="inlineStr">
+      <c r="A291" s="6" t="inlineStr">
         <is>
           <t>test reprise</t>
         </is>
       </c>
-      <c r="B291" t="inlineStr">
+      <c r="B291" s="1" t="inlineStr">
         <is>
           <t>statut_test_reprise</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
+      <c r="C291" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D291" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="292">
-      <c r="A292" t="inlineStr">
+      <c r="A292" s="7" t="inlineStr">
         <is>
           <t>test restauration</t>
         </is>
       </c>
-      <c r="B292" t="inlineStr">
+      <c r="B292" s="8" t="inlineStr">
         <is>
           <t>statut_test_reprise</t>
         </is>
       </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
+      <c r="C292" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D292" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" t="inlineStr">
+      <c r="A293" s="6" t="inlineStr">
         <is>
           <t>backup media</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr">
+      <c r="B293" s="1" t="inlineStr">
         <is>
           <t>support_sauvegarde</t>
         </is>
       </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
+      <c r="C293" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D293" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" t="inlineStr">
+      <c r="A294" s="7" t="inlineStr">
         <is>
           <t>media sauvegarde</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr">
+      <c r="B294" s="8" t="inlineStr">
         <is>
           <t>support_sauvegarde</t>
         </is>
       </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
+      <c r="C294" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D294" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" t="inlineStr">
+      <c r="A295" s="6" t="inlineStr">
         <is>
           <t>support backup</t>
         </is>
       </c>
-      <c r="B295" t="inlineStr">
+      <c r="B295" s="1" t="inlineStr">
         <is>
           <t>support_sauvegarde</t>
         </is>
       </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
+      <c r="C295" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D295" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="inlineStr">
+      <c r="A296" s="7" t="inlineStr">
         <is>
           <t>support sauvegarde</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr">
+      <c r="B296" s="8" t="inlineStr">
         <is>
           <t>support_sauvegarde</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
+      <c r="C296" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D296" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" t="inlineStr">
+      <c r="A297" s="6" t="inlineStr">
         <is>
           <t>support_sauvegarde</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr">
+      <c r="B297" s="1" t="inlineStr">
         <is>
           <t>support_sauvegarde</t>
         </is>
       </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
+      <c r="C297" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D297" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="inlineStr">
+      <c r="A298" s="7" t="inlineStr">
         <is>
           <t>interet</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr">
+      <c r="B298" s="8" t="inlineStr">
         <is>
           <t>taux_interet</t>
         </is>
       </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
+      <c r="C298" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D298" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="299">
-      <c r="A299" t="inlineStr">
+      <c r="A299" s="6" t="inlineStr">
         <is>
           <t>taux</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr">
+      <c r="B299" s="1" t="inlineStr">
         <is>
           <t>taux_interet</t>
         </is>
       </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
+      <c r="C299" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D299" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="inlineStr">
+      <c r="A300" s="7" t="inlineStr">
         <is>
           <t>taux_interet</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
+      <c r="B300" s="8" t="inlineStr">
         <is>
           <t>taux_interet</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
+      <c r="C300" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D300" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="inlineStr">
+      <c r="A301" s="6" t="inlineStr">
         <is>
           <t>contact</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
+      <c r="B301" s="1" t="inlineStr">
         <is>
           <t>telephone</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
+      <c r="C301" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D301" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="302">
-      <c r="A302" t="inlineStr">
+      <c r="A302" s="7" t="inlineStr">
         <is>
           <t>num telephone</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr">
+      <c r="B302" s="8" t="inlineStr">
         <is>
           <t>telephone</t>
         </is>
       </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
+      <c r="C302" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D302" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="303">
-      <c r="A303" t="inlineStr">
+      <c r="A303" s="6" t="inlineStr">
         <is>
           <t>numero telephone</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr">
+      <c r="B303" s="1" t="inlineStr">
         <is>
           <t>telephone</t>
         </is>
       </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
+      <c r="C303" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D303" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="304">
-      <c r="A304" t="inlineStr">
+      <c r="A304" s="7" t="inlineStr">
         <is>
           <t>telephone</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr">
+      <c r="B304" s="8" t="inlineStr">
         <is>
           <t>telephone</t>
         </is>
       </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
+      <c r="C304" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D304" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="305">
-      <c r="A305" t="inlineStr">
+      <c r="A305" s="6" t="inlineStr">
         <is>
           <t>caissier tresorerie</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
+      <c r="B305" s="1" t="inlineStr">
         <is>
           <t>tresorier</t>
         </is>
       </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
+      <c r="C305" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D305" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="306">
-      <c r="A306" t="inlineStr">
+      <c r="A306" s="7" t="inlineStr">
         <is>
           <t>tresorier</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr">
+      <c r="B306" s="8" t="inlineStr">
         <is>
           <t>tresorier</t>
         </is>
       </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
+      <c r="C306" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D306" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="307">
-      <c r="A307" t="inlineStr">
+      <c r="A307" s="6" t="inlineStr">
         <is>
           <t>nature client</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr">
+      <c r="B307" s="1" t="inlineStr">
         <is>
           <t>type_client</t>
         </is>
       </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
+      <c r="C307" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D307" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="308">
-      <c r="A308" t="inlineStr">
+      <c r="A308" s="7" t="inlineStr">
         <is>
           <t>type_client</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr">
+      <c r="B308" s="8" t="inlineStr">
         <is>
           <t>type_client</t>
         </is>
       </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
+      <c r="C308" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D308" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="309">
-      <c r="A309" t="inlineStr">
+      <c r="A309" s="6" t="inlineStr">
         <is>
           <t>nature_operation</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr">
+      <c r="B309" s="1" t="inlineStr">
         <is>
           <t>type_operation</t>
         </is>
       </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
+      <c r="C309" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D309" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="310">
-      <c r="A310" t="inlineStr">
+      <c r="A310" s="7" t="inlineStr">
         <is>
           <t>operation</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr">
+      <c r="B310" s="8" t="inlineStr">
         <is>
           <t>type_operation</t>
         </is>
       </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
+      <c r="C310" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D310" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="311">
-      <c r="A311" t="inlineStr">
+      <c r="A311" s="6" t="inlineStr">
         <is>
           <t>type_operation</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr">
+      <c r="B311" s="1" t="inlineStr">
         <is>
           <t>type_operation</t>
         </is>
       </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
+      <c r="C311" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D311" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="312">
-      <c r="A312" t="inlineStr">
+      <c r="A312" s="7" t="inlineStr">
         <is>
           <t>categorie_produit</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr">
+      <c r="B312" s="8" t="inlineStr">
         <is>
           <t>type_produit</t>
         </is>
       </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
+      <c r="C312" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D312" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="313">
-      <c r="A313" t="inlineStr">
+      <c r="A313" s="6" t="inlineStr">
         <is>
           <t>produit</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr">
+      <c r="B313" s="1" t="inlineStr">
         <is>
           <t>type_produit</t>
         </is>
       </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
+      <c r="C313" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D313" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="314">
-      <c r="A314" t="inlineStr">
+      <c r="A314" s="7" t="inlineStr">
         <is>
           <t>type_credit</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr">
+      <c r="B314" s="8" t="inlineStr">
         <is>
           <t>type_produit</t>
         </is>
       </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
+      <c r="C314" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D314" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="315">
-      <c r="A315" t="inlineStr">
+      <c r="A315" s="6" t="inlineStr">
         <is>
           <t>type_produit</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr">
+      <c r="B315" s="1" t="inlineStr">
         <is>
           <t>type_produit</t>
         </is>
       </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
+      <c r="C315" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D315" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="316">
-      <c r="A316" t="inlineStr">
+      <c r="A316" s="7" t="inlineStr">
         <is>
           <t>backup type</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr">
+      <c r="B316" s="8" t="inlineStr">
         <is>
           <t>type_sauvegarde</t>
         </is>
       </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
+      <c r="C316" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D316" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="317">
-      <c r="A317" t="inlineStr">
+      <c r="A317" s="6" t="inlineStr">
         <is>
           <t>nature sauvegarde</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr">
+      <c r="B317" s="1" t="inlineStr">
         <is>
           <t>type_sauvegarde</t>
         </is>
       </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
+      <c r="C317" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D317" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="318">
-      <c r="A318" t="inlineStr">
+      <c r="A318" s="7" t="inlineStr">
         <is>
           <t>type sauvegarde</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr">
+      <c r="B318" s="8" t="inlineStr">
         <is>
           <t>type_sauvegarde</t>
         </is>
       </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
+      <c r="C318" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D318" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="319">
-      <c r="A319" t="inlineStr">
+      <c r="A319" s="6" t="inlineStr">
         <is>
           <t>type_sauvegarde</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr">
+      <c r="B319" s="1" t="inlineStr">
         <is>
           <t>type_sauvegarde</t>
         </is>
       </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
+      <c r="C319" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D319" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="320">
-      <c r="A320" t="inlineStr">
+      <c r="A320" s="7" t="inlineStr">
         <is>
           <t>age_unit</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr">
+      <c r="B320" s="8" t="inlineStr">
         <is>
           <t>unite_age</t>
         </is>
       </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
+      <c r="C320" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D320" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" t="inlineStr">
+      <c r="A321" s="6" t="inlineStr">
         <is>
           <t>unite_age</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr">
+      <c r="B321" s="1" t="inlineStr">
         <is>
           <t>unite_age</t>
         </is>
       </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
+      <c r="C321" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D321" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" t="inlineStr">
+      <c r="A322" s="7" t="inlineStr">
         <is>
           <t>unité d'age</t>
         </is>
       </c>
-      <c r="B322" t="inlineStr">
+      <c r="B322" s="8" t="inlineStr">
         <is>
           <t>unite_age</t>
         </is>
       </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
+      <c r="C322" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D322" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="A323" t="inlineStr">
+      <c r="A323" s="6" t="inlineStr">
         <is>
           <t>unité d’âge</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr">
+      <c r="B323" s="1" t="inlineStr">
         <is>
           <t>unite_age</t>
         </is>
       </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
+      <c r="C323" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D323" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" t="inlineStr">
+      <c r="A324" s="7" t="inlineStr">
         <is>
           <t>localite</t>
         </is>
       </c>
-      <c r="B324" t="inlineStr">
+      <c r="B324" s="8" t="inlineStr">
         <is>
           <t>zone_geographique</t>
         </is>
       </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
+      <c r="C324" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D324" s="8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" t="inlineStr">
+      <c r="A325" s="6" t="inlineStr">
         <is>
           <t>zone_geographique</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr">
+      <c r="B325" s="1" t="inlineStr">
         <is>
           <t>zone_geographique</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
+      <c r="C325" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D325" s="1" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -12682,10 +12705,28 @@
         </is>
       </c>
     </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>code_produit</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>code_produit</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Perfect Vision</t>
+        </is>
+      </c>
+      <c r="D578" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:D579"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
--- a/data/Rename_columns.xlsx
+++ b/data/Rename_columns.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2546" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2642" uniqueCount="751">
   <si>
     <t>Original</t>
   </si>
@@ -1990,6 +1990,102 @@
     <t>disponible</t>
   </si>
   <si>
+    <t>client_key</t>
+  </si>
+  <si>
+    <t>numero_telephone</t>
+  </si>
+  <si>
+    <t>date_creation_client</t>
+  </si>
+  <si>
+    <t>sources_client</t>
+  </si>
+  <si>
+    <t>methode_rapprochement</t>
+  </si>
+  <si>
+    <t>statut_confiance</t>
+  </si>
+  <si>
+    <t>present_customers</t>
+  </si>
+  <si>
+    <t>date_derniere_operation_observee</t>
+  </si>
+  <si>
+    <t>jours_depuis_derniere_operation</t>
+  </si>
+  <si>
+    <t>nombre_operations</t>
+  </si>
+  <si>
+    <t>nombre_periodes_actives</t>
+  </si>
+  <si>
+    <t>actif_periode</t>
+  </si>
+  <si>
+    <t>nouveau_client</t>
+  </si>
+  <si>
+    <t>nouveau_client_actif</t>
+  </si>
+  <si>
+    <t>sans_mouvement_periode</t>
+  </si>
+  <si>
+    <t>historique_insuffisant</t>
+  </si>
+  <si>
+    <t>inactif_observe</t>
+  </si>
+  <si>
+    <t>presence_epargne</t>
+  </si>
+  <si>
+    <t>presence_dat</t>
+  </si>
+  <si>
+    <t>presence_credit</t>
+  </si>
+  <si>
+    <t>presence_transaction</t>
+  </si>
+  <si>
+    <t>multi_produits</t>
+  </si>
+  <si>
+    <t>segment_produit</t>
+  </si>
+  <si>
+    <t>segment_client</t>
+  </si>
+  <si>
+    <t>clients_referentiel</t>
+  </si>
+  <si>
+    <t>clients_connus_solution_numerique</t>
+  </si>
+  <si>
+    <t>clients_actifs</t>
+  </si>
+  <si>
+    <t>taux_clients_actifs</t>
+  </si>
+  <si>
+    <t>nouveaux_clients</t>
+  </si>
+  <si>
+    <t>nouveaux_clients_actifs</t>
+  </si>
+  <si>
+    <t>taux_activation_nouveaux_clients</t>
+  </si>
+  <si>
+    <t>clients_sans_mouvement</t>
+  </si>
+  <si>
     <t>code_agent</t>
   </si>
   <si>
@@ -2020,9 +2116,6 @@
     <t>id_operation_mere</t>
   </si>
   <si>
-    <t>numero_telephone</t>
-  </si>
-  <si>
     <t>date_creation</t>
   </si>
   <si>
@@ -2135,6 +2228,18 @@
   </si>
   <si>
     <t>situation</t>
+  </si>
+  <si>
+    <t>cle_client</t>
+  </si>
+  <si>
+    <t>present_dans_customers</t>
+  </si>
+  <si>
+    <t>date_derniere_operation</t>
+  </si>
+  <si>
+    <t>actif_sur_periode</t>
   </si>
   <si>
     <t>Standard</t>
@@ -2519,7 +2624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D656"/>
+  <dimension ref="A1:D688"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2544,10 +2649,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D2" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2558,10 +2663,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D3" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2572,10 +2677,10 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D4" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2586,10 +2691,10 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D5" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2600,10 +2705,10 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D6" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2614,10 +2719,10 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D7" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2628,10 +2733,10 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D8" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2642,10 +2747,10 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D9" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2656,10 +2761,10 @@
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D10" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2670,10 +2775,10 @@
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D11" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2684,10 +2789,10 @@
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D12" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2698,10 +2803,10 @@
         <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D13" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2712,10 +2817,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D14" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2726,10 +2831,10 @@
         <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D15" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2740,10 +2845,10 @@
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D16" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2754,10 +2859,10 @@
         <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D17" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2768,10 +2873,10 @@
         <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D18" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2782,10 +2887,10 @@
         <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D19" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2796,10 +2901,10 @@
         <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D20" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2810,10 +2915,10 @@
         <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D21" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2821,13 +2926,13 @@
         <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>658</v>
+        <v>690</v>
       </c>
       <c r="C22" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D22" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2838,10 +2943,10 @@
         <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D23" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2852,10 +2957,10 @@
         <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D24" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2866,10 +2971,10 @@
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D25" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2880,10 +2985,10 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D26" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2894,10 +2999,10 @@
         <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D27" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2908,10 +3013,10 @@
         <v>30</v>
       </c>
       <c r="C28" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D28" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2922,10 +3027,10 @@
         <v>30</v>
       </c>
       <c r="C29" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D29" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2936,10 +3041,10 @@
         <v>30</v>
       </c>
       <c r="C30" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D30" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2950,10 +3055,10 @@
         <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D31" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2964,10 +3069,10 @@
         <v>35</v>
       </c>
       <c r="C32" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D32" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2978,10 +3083,10 @@
         <v>35</v>
       </c>
       <c r="C33" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D33" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2992,10 +3097,10 @@
         <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D34" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -3006,10 +3111,10 @@
         <v>35</v>
       </c>
       <c r="C35" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D35" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -3020,10 +3125,10 @@
         <v>39</v>
       </c>
       <c r="C36" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D36" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -3034,10 +3139,10 @@
         <v>39</v>
       </c>
       <c r="C37" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D37" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -3048,10 +3153,10 @@
         <v>39</v>
       </c>
       <c r="C38" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D38" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -3062,10 +3167,10 @@
         <v>39</v>
       </c>
       <c r="C39" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D39" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3076,10 +3181,10 @@
         <v>39</v>
       </c>
       <c r="C40" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D40" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3090,10 +3195,10 @@
         <v>43</v>
       </c>
       <c r="C41" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D41" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3104,10 +3209,10 @@
         <v>43</v>
       </c>
       <c r="C42" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D42" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3118,10 +3223,10 @@
         <v>45</v>
       </c>
       <c r="C43" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D43" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3132,10 +3237,10 @@
         <v>49</v>
       </c>
       <c r="C44" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D44" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3146,10 +3251,10 @@
         <v>45</v>
       </c>
       <c r="C45" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D45" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3160,10 +3265,10 @@
         <v>45</v>
       </c>
       <c r="C46" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D46" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3174,10 +3279,10 @@
         <v>49</v>
       </c>
       <c r="C47" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D47" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3188,10 +3293,10 @@
         <v>45</v>
       </c>
       <c r="C48" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D48" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3202,10 +3307,10 @@
         <v>51</v>
       </c>
       <c r="C49" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D49" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3216,10 +3321,10 @@
         <v>51</v>
       </c>
       <c r="C50" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D50" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3230,10 +3335,10 @@
         <v>51</v>
       </c>
       <c r="C51" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D51" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3244,10 +3349,10 @@
         <v>51</v>
       </c>
       <c r="C52" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D52" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3258,10 +3363,10 @@
         <v>55</v>
       </c>
       <c r="C53" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D53" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3272,10 +3377,10 @@
         <v>56</v>
       </c>
       <c r="C54" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D54" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3286,10 +3391,10 @@
         <v>55</v>
       </c>
       <c r="C55" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D55" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3300,10 +3405,10 @@
         <v>58</v>
       </c>
       <c r="C56" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D56" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3314,10 +3419,10 @@
         <v>59</v>
       </c>
       <c r="C57" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D57" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3328,10 +3433,10 @@
         <v>60</v>
       </c>
       <c r="C58" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D58" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3342,10 +3447,10 @@
         <v>61</v>
       </c>
       <c r="C59" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D59" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3356,10 +3461,10 @@
         <v>61</v>
       </c>
       <c r="C60" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D60" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3370,10 +3475,10 @@
         <v>61</v>
       </c>
       <c r="C61" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D61" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3384,10 +3489,10 @@
         <v>61</v>
       </c>
       <c r="C62" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D62" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3398,10 +3503,10 @@
         <v>61</v>
       </c>
       <c r="C63" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D63" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3412,10 +3517,10 @@
         <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D64" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3426,10 +3531,10 @@
         <v>68</v>
       </c>
       <c r="C65" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D65" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3440,10 +3545,10 @@
         <v>68</v>
       </c>
       <c r="C66" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D66" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3454,10 +3559,10 @@
         <v>68</v>
       </c>
       <c r="C67" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D67" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3468,10 +3573,10 @@
         <v>68</v>
       </c>
       <c r="C68" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D68" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3482,10 +3587,10 @@
         <v>73</v>
       </c>
       <c r="C69" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D69" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3496,10 +3601,10 @@
         <v>73</v>
       </c>
       <c r="C70" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D70" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3510,10 +3615,10 @@
         <v>73</v>
       </c>
       <c r="C71" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D71" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3524,10 +3629,10 @@
         <v>73</v>
       </c>
       <c r="C72" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D72" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3538,10 +3643,10 @@
         <v>73</v>
       </c>
       <c r="C73" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D73" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3552,10 +3657,10 @@
         <v>73</v>
       </c>
       <c r="C74" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D74" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3566,10 +3671,10 @@
         <v>78</v>
       </c>
       <c r="C75" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D75" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3580,10 +3685,10 @@
         <v>78</v>
       </c>
       <c r="C76" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D76" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3594,10 +3699,10 @@
         <v>80</v>
       </c>
       <c r="C77" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D77" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3608,10 +3713,10 @@
         <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D78" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3622,10 +3727,10 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D79" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3636,10 +3741,10 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D80" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3650,10 +3755,10 @@
         <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D81" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3664,10 +3769,10 @@
         <v>85</v>
       </c>
       <c r="C82" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D82" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3678,10 +3783,10 @@
         <v>85</v>
       </c>
       <c r="C83" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D83" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3692,10 +3797,10 @@
         <v>85</v>
       </c>
       <c r="C84" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D84" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3706,10 +3811,10 @@
         <v>85</v>
       </c>
       <c r="C85" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D85" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3720,10 +3825,10 @@
         <v>91</v>
       </c>
       <c r="C86" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D86" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3734,10 +3839,10 @@
         <v>91</v>
       </c>
       <c r="C87" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D87" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3745,13 +3850,13 @@
         <v>90</v>
       </c>
       <c r="B88" t="s">
-        <v>659</v>
+        <v>691</v>
       </c>
       <c r="C88" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D88" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3762,10 +3867,10 @@
         <v>91</v>
       </c>
       <c r="C89" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D89" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3776,10 +3881,10 @@
         <v>93</v>
       </c>
       <c r="C90" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D90" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3790,10 +3895,10 @@
         <v>93</v>
       </c>
       <c r="C91" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D91" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3804,10 +3909,10 @@
         <v>93</v>
       </c>
       <c r="C92" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D92" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3818,10 +3923,10 @@
         <v>98</v>
       </c>
       <c r="C93" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D93" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3832,10 +3937,10 @@
         <v>98</v>
       </c>
       <c r="C94" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D94" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3846,10 +3951,10 @@
         <v>98</v>
       </c>
       <c r="C95" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D95" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3860,10 +3965,10 @@
         <v>98</v>
       </c>
       <c r="C96" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D96" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3874,10 +3979,10 @@
         <v>103</v>
       </c>
       <c r="C97" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D97" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3888,10 +3993,10 @@
         <v>103</v>
       </c>
       <c r="C98" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D98" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3902,10 +4007,10 @@
         <v>103</v>
       </c>
       <c r="C99" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D99" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3916,10 +4021,10 @@
         <v>103</v>
       </c>
       <c r="C100" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D100" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3930,10 +4035,10 @@
         <v>103</v>
       </c>
       <c r="C101" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D101" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3944,10 +4049,10 @@
         <v>103</v>
       </c>
       <c r="C102" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D102" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3958,10 +4063,10 @@
         <v>107</v>
       </c>
       <c r="C103" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D103" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3972,10 +4077,10 @@
         <v>107</v>
       </c>
       <c r="C104" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D104" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3986,10 +4091,10 @@
         <v>107</v>
       </c>
       <c r="C105" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D105" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -4000,10 +4105,10 @@
         <v>107</v>
       </c>
       <c r="C106" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D106" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -4014,10 +4119,10 @@
         <v>112</v>
       </c>
       <c r="C107" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D107" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -4028,10 +4133,10 @@
         <v>112</v>
       </c>
       <c r="C108" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D108" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -4042,10 +4147,10 @@
         <v>112</v>
       </c>
       <c r="C109" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D109" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -4056,10 +4161,10 @@
         <v>112</v>
       </c>
       <c r="C110" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D110" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -4070,10 +4175,10 @@
         <v>112</v>
       </c>
       <c r="C111" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D111" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -4084,10 +4189,10 @@
         <v>117</v>
       </c>
       <c r="C112" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D112" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -4098,10 +4203,10 @@
         <v>117</v>
       </c>
       <c r="C113" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D113" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4112,10 +4217,10 @@
         <v>117</v>
       </c>
       <c r="C114" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D114" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4126,10 +4231,10 @@
         <v>117</v>
       </c>
       <c r="C115" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D115" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4140,10 +4245,10 @@
         <v>119</v>
       </c>
       <c r="C116" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D116" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4154,10 +4259,10 @@
         <v>119</v>
       </c>
       <c r="C117" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D117" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4168,10 +4273,10 @@
         <v>119</v>
       </c>
       <c r="C118" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D118" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4182,10 +4287,10 @@
         <v>121</v>
       </c>
       <c r="C119" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D119" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4196,10 +4301,10 @@
         <v>121</v>
       </c>
       <c r="C120" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D120" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4210,10 +4315,10 @@
         <v>121</v>
       </c>
       <c r="C121" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D121" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4224,10 +4329,10 @@
         <v>126</v>
       </c>
       <c r="C122" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D122" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4238,10 +4343,10 @@
         <v>126</v>
       </c>
       <c r="C123" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D123" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4252,10 +4357,10 @@
         <v>126</v>
       </c>
       <c r="C124" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D124" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4266,10 +4371,10 @@
         <v>126</v>
       </c>
       <c r="C125" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D125" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4280,10 +4385,10 @@
         <v>126</v>
       </c>
       <c r="C126" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D126" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4294,10 +4399,10 @@
         <v>133</v>
       </c>
       <c r="C127" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D127" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4308,10 +4413,10 @@
         <v>133</v>
       </c>
       <c r="C128" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D128" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4322,10 +4427,10 @@
         <v>133</v>
       </c>
       <c r="C129" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D129" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4336,10 +4441,10 @@
         <v>133</v>
       </c>
       <c r="C130" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D130" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4350,10 +4455,10 @@
         <v>133</v>
       </c>
       <c r="C131" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D131" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4364,10 +4469,10 @@
         <v>137</v>
       </c>
       <c r="C132" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D132" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4378,10 +4483,10 @@
         <v>137</v>
       </c>
       <c r="C133" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D133" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4392,10 +4497,10 @@
         <v>137</v>
       </c>
       <c r="C134" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D134" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4406,10 +4511,10 @@
         <v>137</v>
       </c>
       <c r="C135" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D135" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4420,10 +4525,10 @@
         <v>137</v>
       </c>
       <c r="C136" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D136" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4434,10 +4539,10 @@
         <v>143</v>
       </c>
       <c r="C137" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D137" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4448,10 +4553,10 @@
         <v>143</v>
       </c>
       <c r="C138" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D138" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4462,10 +4567,10 @@
         <v>143</v>
       </c>
       <c r="C139" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D139" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4476,10 +4581,10 @@
         <v>143</v>
       </c>
       <c r="C140" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D140" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4490,10 +4595,10 @@
         <v>143</v>
       </c>
       <c r="C141" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D141" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4504,10 +4609,10 @@
         <v>143</v>
       </c>
       <c r="C142" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D142" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4518,10 +4623,10 @@
         <v>145</v>
       </c>
       <c r="C143" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D143" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4532,10 +4637,10 @@
         <v>145</v>
       </c>
       <c r="C144" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D144" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4546,10 +4651,10 @@
         <v>145</v>
       </c>
       <c r="C145" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D145" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4560,10 +4665,10 @@
         <v>145</v>
       </c>
       <c r="C146" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D146" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4574,10 +4679,10 @@
         <v>149</v>
       </c>
       <c r="C147" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D147" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4588,10 +4693,10 @@
         <v>149</v>
       </c>
       <c r="C148" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D148" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4602,10 +4707,10 @@
         <v>149</v>
       </c>
       <c r="C149" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D149" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4616,10 +4721,10 @@
         <v>149</v>
       </c>
       <c r="C150" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D150" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4630,10 +4735,10 @@
         <v>153</v>
       </c>
       <c r="C151" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D151" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4644,10 +4749,10 @@
         <v>157</v>
       </c>
       <c r="C152" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D152" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4658,10 +4763,10 @@
         <v>157</v>
       </c>
       <c r="C153" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D153" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4672,10 +4777,10 @@
         <v>157</v>
       </c>
       <c r="C154" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D154" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4686,10 +4791,10 @@
         <v>157</v>
       </c>
       <c r="C155" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D155" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4700,10 +4805,10 @@
         <v>157</v>
       </c>
       <c r="C156" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D156" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4714,10 +4819,10 @@
         <v>161</v>
       </c>
       <c r="C157" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D157" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4728,10 +4833,10 @@
         <v>161</v>
       </c>
       <c r="C158" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D158" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4742,10 +4847,10 @@
         <v>161</v>
       </c>
       <c r="C159" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D159" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4756,10 +4861,10 @@
         <v>161</v>
       </c>
       <c r="C160" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D160" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4770,10 +4875,10 @@
         <v>161</v>
       </c>
       <c r="C161" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D161" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4784,10 +4889,10 @@
         <v>165</v>
       </c>
       <c r="C162" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D162" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4798,10 +4903,10 @@
         <v>165</v>
       </c>
       <c r="C163" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D163" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4812,10 +4917,10 @@
         <v>165</v>
       </c>
       <c r="C164" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D164" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4826,10 +4931,10 @@
         <v>165</v>
       </c>
       <c r="C165" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D165" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4840,10 +4945,10 @@
         <v>169</v>
       </c>
       <c r="C166" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D166" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4854,10 +4959,10 @@
         <v>169</v>
       </c>
       <c r="C167" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D167" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4868,10 +4973,10 @@
         <v>169</v>
       </c>
       <c r="C168" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D168" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4879,13 +4984,13 @@
         <v>171</v>
       </c>
       <c r="B169" t="s">
-        <v>660</v>
+        <v>692</v>
       </c>
       <c r="C169" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D169" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4893,13 +4998,13 @@
         <v>172</v>
       </c>
       <c r="B170" t="s">
-        <v>660</v>
+        <v>692</v>
       </c>
       <c r="C170" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D170" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4910,10 +5015,10 @@
         <v>176</v>
       </c>
       <c r="C171" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D171" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4924,10 +5029,10 @@
         <v>176</v>
       </c>
       <c r="C172" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D172" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4938,10 +5043,10 @@
         <v>176</v>
       </c>
       <c r="C173" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D173" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4952,10 +5057,10 @@
         <v>176</v>
       </c>
       <c r="C174" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D174" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4966,10 +5071,10 @@
         <v>182</v>
       </c>
       <c r="C175" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D175" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4980,10 +5085,10 @@
         <v>182</v>
       </c>
       <c r="C176" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D176" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4994,10 +5099,10 @@
         <v>182</v>
       </c>
       <c r="C177" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D177" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -5008,10 +5113,10 @@
         <v>182</v>
       </c>
       <c r="C178" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D178" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -5022,10 +5127,10 @@
         <v>182</v>
       </c>
       <c r="C179" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D179" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -5036,10 +5141,10 @@
         <v>182</v>
       </c>
       <c r="C180" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D180" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -5050,10 +5155,10 @@
         <v>188</v>
       </c>
       <c r="C181" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D181" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -5064,10 +5169,10 @@
         <v>188</v>
       </c>
       <c r="C182" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D182" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -5078,10 +5183,10 @@
         <v>188</v>
       </c>
       <c r="C183" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D183" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -5092,10 +5197,10 @@
         <v>188</v>
       </c>
       <c r="C184" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D184" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -5106,10 +5211,10 @@
         <v>188</v>
       </c>
       <c r="C185" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D185" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5120,10 +5225,10 @@
         <v>188</v>
       </c>
       <c r="C186" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D186" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5134,10 +5239,10 @@
         <v>191</v>
       </c>
       <c r="C187" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D187" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5148,10 +5253,10 @@
         <v>191</v>
       </c>
       <c r="C188" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D188" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5162,10 +5267,10 @@
         <v>191</v>
       </c>
       <c r="C189" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D189" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5176,10 +5281,10 @@
         <v>191</v>
       </c>
       <c r="C190" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D190" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5190,10 +5295,10 @@
         <v>193</v>
       </c>
       <c r="C191" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D191" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5204,10 +5309,10 @@
         <v>193</v>
       </c>
       <c r="C192" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D192" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5215,13 +5320,13 @@
         <v>195</v>
       </c>
       <c r="B193" t="s">
-        <v>661</v>
+        <v>693</v>
       </c>
       <c r="C193" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D193" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5229,13 +5334,13 @@
         <v>196</v>
       </c>
       <c r="B194" t="s">
-        <v>661</v>
+        <v>693</v>
       </c>
       <c r="C194" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D194" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5246,10 +5351,10 @@
         <v>201</v>
       </c>
       <c r="C195" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D195" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5260,10 +5365,10 @@
         <v>201</v>
       </c>
       <c r="C196" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D196" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5274,10 +5379,10 @@
         <v>201</v>
       </c>
       <c r="C197" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D197" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5288,10 +5393,10 @@
         <v>201</v>
       </c>
       <c r="C198" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D198" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5302,10 +5407,10 @@
         <v>201</v>
       </c>
       <c r="C199" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D199" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5316,10 +5421,10 @@
         <v>203</v>
       </c>
       <c r="C200" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D200" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5330,10 +5435,10 @@
         <v>203</v>
       </c>
       <c r="C201" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D201" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5344,10 +5449,10 @@
         <v>203</v>
       </c>
       <c r="C202" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D202" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5358,10 +5463,10 @@
         <v>208</v>
       </c>
       <c r="C203" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D203" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5372,10 +5477,10 @@
         <v>208</v>
       </c>
       <c r="C204" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D204" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5386,10 +5491,10 @@
         <v>208</v>
       </c>
       <c r="C205" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D205" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5400,10 +5505,10 @@
         <v>208</v>
       </c>
       <c r="C206" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D206" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5414,10 +5519,10 @@
         <v>208</v>
       </c>
       <c r="C207" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D207" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5428,10 +5533,10 @@
         <v>213</v>
       </c>
       <c r="C208" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D208" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5442,10 +5547,10 @@
         <v>213</v>
       </c>
       <c r="C209" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D209" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5456,10 +5561,10 @@
         <v>213</v>
       </c>
       <c r="C210" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D210" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5470,10 +5575,10 @@
         <v>213</v>
       </c>
       <c r="C211" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D211" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5484,10 +5589,10 @@
         <v>121</v>
       </c>
       <c r="C212" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D212" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5498,10 +5603,10 @@
         <v>214</v>
       </c>
       <c r="C213" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D213" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5512,10 +5617,10 @@
         <v>218</v>
       </c>
       <c r="C214" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D214" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5526,10 +5631,10 @@
         <v>218</v>
       </c>
       <c r="C215" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D215" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5540,10 +5645,10 @@
         <v>218</v>
       </c>
       <c r="C216" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D216" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5554,10 +5659,10 @@
         <v>218</v>
       </c>
       <c r="C217" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D217" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5568,10 +5673,10 @@
         <v>218</v>
       </c>
       <c r="C218" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D218" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5582,10 +5687,10 @@
         <v>222</v>
       </c>
       <c r="C219" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D219" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5596,10 +5701,10 @@
         <v>222</v>
       </c>
       <c r="C220" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D220" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5610,10 +5715,10 @@
         <v>222</v>
       </c>
       <c r="C221" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D221" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5624,10 +5729,10 @@
         <v>228</v>
       </c>
       <c r="C222" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D222" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5638,10 +5743,10 @@
         <v>228</v>
       </c>
       <c r="C223" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D223" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5652,10 +5757,10 @@
         <v>228</v>
       </c>
       <c r="C224" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D224" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5666,10 +5771,10 @@
         <v>228</v>
       </c>
       <c r="C225" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D225" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5680,10 +5785,10 @@
         <v>228</v>
       </c>
       <c r="C226" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D226" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5694,10 +5799,10 @@
         <v>228</v>
       </c>
       <c r="C227" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D227" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5708,10 +5813,10 @@
         <v>234</v>
       </c>
       <c r="C228" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D228" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5722,10 +5827,10 @@
         <v>234</v>
       </c>
       <c r="C229" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D229" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5736,10 +5841,10 @@
         <v>234</v>
       </c>
       <c r="C230" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D230" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5750,10 +5855,10 @@
         <v>234</v>
       </c>
       <c r="C231" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D231" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5764,10 +5869,10 @@
         <v>234</v>
       </c>
       <c r="C232" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D232" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5778,10 +5883,10 @@
         <v>234</v>
       </c>
       <c r="C233" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D233" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5792,10 +5897,10 @@
         <v>240</v>
       </c>
       <c r="C234" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D234" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5806,10 +5911,10 @@
         <v>240</v>
       </c>
       <c r="C235" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D235" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5820,10 +5925,10 @@
         <v>240</v>
       </c>
       <c r="C236" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D236" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5834,10 +5939,10 @@
         <v>240</v>
       </c>
       <c r="C237" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D237" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5848,10 +5953,10 @@
         <v>240</v>
       </c>
       <c r="C238" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D238" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5862,10 +5967,10 @@
         <v>243</v>
       </c>
       <c r="C239" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D239" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5876,10 +5981,10 @@
         <v>243</v>
       </c>
       <c r="C240" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D240" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5890,10 +5995,10 @@
         <v>243</v>
       </c>
       <c r="C241" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D241" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5904,10 +6009,10 @@
         <v>243</v>
       </c>
       <c r="C242" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D242" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5918,10 +6023,10 @@
         <v>245</v>
       </c>
       <c r="C243" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D243" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5932,10 +6037,10 @@
         <v>245</v>
       </c>
       <c r="C244" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D244" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5946,10 +6051,10 @@
         <v>245</v>
       </c>
       <c r="C245" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D245" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5960,10 +6065,10 @@
         <v>245</v>
       </c>
       <c r="C246" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D246" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5974,10 +6079,10 @@
         <v>245</v>
       </c>
       <c r="C247" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D247" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5988,10 +6093,10 @@
         <v>245</v>
       </c>
       <c r="C248" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D248" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -6002,10 +6107,10 @@
         <v>253</v>
       </c>
       <c r="C249" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D249" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -6016,10 +6121,10 @@
         <v>253</v>
       </c>
       <c r="C250" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D250" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -6030,10 +6135,10 @@
         <v>253</v>
       </c>
       <c r="C251" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D251" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -6044,10 +6149,10 @@
         <v>253</v>
       </c>
       <c r="C252" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D252" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -6058,10 +6163,10 @@
         <v>257</v>
       </c>
       <c r="C253" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D253" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -6072,10 +6177,10 @@
         <v>257</v>
       </c>
       <c r="C254" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D254" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -6086,10 +6191,10 @@
         <v>257</v>
       </c>
       <c r="C255" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D255" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -6100,10 +6205,10 @@
         <v>257</v>
       </c>
       <c r="C256" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D256" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -6114,10 +6219,10 @@
         <v>257</v>
       </c>
       <c r="C257" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D257" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -6128,10 +6233,10 @@
         <v>262</v>
       </c>
       <c r="C258" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D258" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -6142,10 +6247,10 @@
         <v>262</v>
       </c>
       <c r="C259" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D259" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -6156,10 +6261,10 @@
         <v>262</v>
       </c>
       <c r="C260" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D260" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -6170,10 +6275,10 @@
         <v>262</v>
       </c>
       <c r="C261" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D261" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -6184,10 +6289,10 @@
         <v>266</v>
       </c>
       <c r="C262" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D262" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -6198,10 +6303,10 @@
         <v>266</v>
       </c>
       <c r="C263" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D263" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -6212,10 +6317,10 @@
         <v>266</v>
       </c>
       <c r="C264" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D264" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -6226,10 +6331,10 @@
         <v>266</v>
       </c>
       <c r="C265" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D265" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -6240,10 +6345,10 @@
         <v>268</v>
       </c>
       <c r="C266" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D266" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -6254,10 +6359,10 @@
         <v>268</v>
       </c>
       <c r="C267" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D267" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -6268,10 +6373,10 @@
         <v>270</v>
       </c>
       <c r="C268" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D268" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -6282,10 +6387,10 @@
         <v>270</v>
       </c>
       <c r="C269" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D269" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -6296,10 +6401,10 @@
         <v>275</v>
       </c>
       <c r="C270" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D270" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -6310,10 +6415,10 @@
         <v>275</v>
       </c>
       <c r="C271" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D271" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -6324,10 +6429,10 @@
         <v>275</v>
       </c>
       <c r="C272" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D272" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -6338,10 +6443,10 @@
         <v>275</v>
       </c>
       <c r="C273" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D273" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -6352,10 +6457,10 @@
         <v>275</v>
       </c>
       <c r="C274" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D274" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -6366,10 +6471,10 @@
         <v>278</v>
       </c>
       <c r="C275" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D275" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -6380,10 +6485,10 @@
         <v>278</v>
       </c>
       <c r="C276" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D276" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -6394,10 +6499,10 @@
         <v>278</v>
       </c>
       <c r="C277" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D277" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -6408,10 +6513,10 @@
         <v>282</v>
       </c>
       <c r="C278" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D278" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -6422,10 +6527,10 @@
         <v>282</v>
       </c>
       <c r="C279" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D279" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -6436,10 +6541,10 @@
         <v>282</v>
       </c>
       <c r="C280" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D280" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -6450,10 +6555,10 @@
         <v>282</v>
       </c>
       <c r="C281" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D281" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -6464,10 +6569,10 @@
         <v>286</v>
       </c>
       <c r="C282" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D282" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -6478,10 +6583,10 @@
         <v>286</v>
       </c>
       <c r="C283" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D283" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -6492,10 +6597,10 @@
         <v>286</v>
       </c>
       <c r="C284" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D284" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -6506,10 +6611,10 @@
         <v>286</v>
       </c>
       <c r="C285" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D285" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -6520,10 +6625,10 @@
         <v>290</v>
       </c>
       <c r="C286" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D286" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -6534,10 +6639,10 @@
         <v>290</v>
       </c>
       <c r="C287" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D287" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -6548,10 +6653,10 @@
         <v>290</v>
       </c>
       <c r="C288" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D288" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -6562,10 +6667,10 @@
         <v>290</v>
       </c>
       <c r="C289" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D289" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -6576,10 +6681,10 @@
         <v>290</v>
       </c>
       <c r="C290" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D290" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -6590,10 +6695,10 @@
         <v>290</v>
       </c>
       <c r="C291" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D291" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -6604,10 +6709,10 @@
         <v>290</v>
       </c>
       <c r="C292" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D292" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -6618,10 +6723,10 @@
         <v>298</v>
       </c>
       <c r="C293" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D293" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -6632,10 +6737,10 @@
         <v>298</v>
       </c>
       <c r="C294" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D294" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -6646,10 +6751,10 @@
         <v>298</v>
       </c>
       <c r="C295" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D295" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -6660,10 +6765,10 @@
         <v>298</v>
       </c>
       <c r="C296" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D296" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -6674,10 +6779,10 @@
         <v>298</v>
       </c>
       <c r="C297" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D297" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -6688,10 +6793,10 @@
         <v>301</v>
       </c>
       <c r="C298" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D298" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -6702,10 +6807,10 @@
         <v>301</v>
       </c>
       <c r="C299" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D299" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -6716,10 +6821,10 @@
         <v>301</v>
       </c>
       <c r="C300" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D300" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -6730,10 +6835,10 @@
         <v>305</v>
       </c>
       <c r="C301" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D301" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -6744,10 +6849,10 @@
         <v>305</v>
       </c>
       <c r="C302" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D302" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -6755,13 +6860,13 @@
         <v>304</v>
       </c>
       <c r="B303" t="s">
-        <v>305</v>
+        <v>659</v>
       </c>
       <c r="C303" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D303" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -6772,10 +6877,10 @@
         <v>305</v>
       </c>
       <c r="C304" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D304" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -6786,10 +6891,10 @@
         <v>307</v>
       </c>
       <c r="C305" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D305" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -6800,10 +6905,10 @@
         <v>307</v>
       </c>
       <c r="C306" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D306" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -6814,10 +6919,10 @@
         <v>309</v>
       </c>
       <c r="C307" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D307" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -6828,10 +6933,10 @@
         <v>309</v>
       </c>
       <c r="C308" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D308" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -6842,10 +6947,10 @@
         <v>312</v>
       </c>
       <c r="C309" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D309" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -6856,10 +6961,10 @@
         <v>312</v>
       </c>
       <c r="C310" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D310" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -6870,10 +6975,10 @@
         <v>312</v>
       </c>
       <c r="C311" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D311" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -6884,10 +6989,10 @@
         <v>316</v>
       </c>
       <c r="C312" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D312" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -6898,10 +7003,10 @@
         <v>316</v>
       </c>
       <c r="C313" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D313" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -6912,10 +7017,10 @@
         <v>316</v>
       </c>
       <c r="C314" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D314" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -6926,10 +7031,10 @@
         <v>316</v>
       </c>
       <c r="C315" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D315" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -6940,10 +7045,10 @@
         <v>320</v>
       </c>
       <c r="C316" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D316" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -6954,10 +7059,10 @@
         <v>320</v>
       </c>
       <c r="C317" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D317" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -6968,10 +7073,10 @@
         <v>320</v>
       </c>
       <c r="C318" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D318" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -6982,10 +7087,10 @@
         <v>320</v>
       </c>
       <c r="C319" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D319" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -6996,10 +7101,10 @@
         <v>322</v>
       </c>
       <c r="C320" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D320" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -7010,10 +7115,10 @@
         <v>322</v>
       </c>
       <c r="C321" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D321" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -7024,10 +7129,10 @@
         <v>322</v>
       </c>
       <c r="C322" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D322" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -7038,10 +7143,10 @@
         <v>322</v>
       </c>
       <c r="C323" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D323" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -7052,10 +7157,10 @@
         <v>326</v>
       </c>
       <c r="C324" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D324" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -7066,10 +7171,10 @@
         <v>326</v>
       </c>
       <c r="C325" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D325" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -7080,10 +7185,10 @@
         <v>55</v>
       </c>
       <c r="C326" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D326" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -7094,10 +7199,10 @@
         <v>56</v>
       </c>
       <c r="C327" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D327" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -7108,10 +7213,10 @@
         <v>208</v>
       </c>
       <c r="C328" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D328" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -7122,10 +7227,10 @@
         <v>208</v>
       </c>
       <c r="C329" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D329" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -7136,10 +7241,10 @@
         <v>208</v>
       </c>
       <c r="C330" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D330" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -7150,10 +7255,10 @@
         <v>121</v>
       </c>
       <c r="C331" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D331" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -7164,10 +7269,10 @@
         <v>98</v>
       </c>
       <c r="C332" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D332" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -7178,10 +7283,10 @@
         <v>107</v>
       </c>
       <c r="C333" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D333" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -7192,10 +7297,10 @@
         <v>107</v>
       </c>
       <c r="C334" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D334" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -7206,10 +7311,10 @@
         <v>107</v>
       </c>
       <c r="C335" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D335" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -7220,10 +7325,10 @@
         <v>107</v>
       </c>
       <c r="C336" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D336" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -7234,10 +7339,10 @@
         <v>107</v>
       </c>
       <c r="C337" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D337" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -7248,10 +7353,10 @@
         <v>107</v>
       </c>
       <c r="C338" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D338" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -7262,10 +7367,10 @@
         <v>107</v>
       </c>
       <c r="C339" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D339" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -7276,10 +7381,10 @@
         <v>107</v>
       </c>
       <c r="C340" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D340" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -7290,10 +7395,10 @@
         <v>107</v>
       </c>
       <c r="C341" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D341" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -7301,13 +7406,13 @@
         <v>343</v>
       </c>
       <c r="B342" t="s">
-        <v>662</v>
+        <v>694</v>
       </c>
       <c r="C342" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D342" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -7318,10 +7423,10 @@
         <v>107</v>
       </c>
       <c r="C343" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D343" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -7332,10 +7437,10 @@
         <v>191</v>
       </c>
       <c r="C344" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D344" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -7346,10 +7451,10 @@
         <v>191</v>
       </c>
       <c r="C345" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D345" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -7360,10 +7465,10 @@
         <v>176</v>
       </c>
       <c r="C346" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D346" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -7374,10 +7479,10 @@
         <v>176</v>
       </c>
       <c r="C347" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D347" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -7388,10 +7493,10 @@
         <v>176</v>
       </c>
       <c r="C348" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D348" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -7402,10 +7507,10 @@
         <v>176</v>
       </c>
       <c r="C349" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D349" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -7416,10 +7521,10 @@
         <v>176</v>
       </c>
       <c r="C350" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D350" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -7430,10 +7535,10 @@
         <v>176</v>
       </c>
       <c r="C351" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D351" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -7444,10 +7549,10 @@
         <v>176</v>
       </c>
       <c r="C352" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D352" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -7458,10 +7563,10 @@
         <v>176</v>
       </c>
       <c r="C353" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D353" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -7472,10 +7577,10 @@
         <v>176</v>
       </c>
       <c r="C354" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D354" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -7486,10 +7591,10 @@
         <v>176</v>
       </c>
       <c r="C355" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D355" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -7500,10 +7605,10 @@
         <v>176</v>
       </c>
       <c r="C356" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D356" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -7514,10 +7619,10 @@
         <v>193</v>
       </c>
       <c r="C357" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D357" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -7528,10 +7633,10 @@
         <v>193</v>
       </c>
       <c r="C358" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D358" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -7542,10 +7647,10 @@
         <v>193</v>
       </c>
       <c r="C359" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D359" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -7556,10 +7661,10 @@
         <v>193</v>
       </c>
       <c r="C360" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D360" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -7570,10 +7675,10 @@
         <v>268</v>
       </c>
       <c r="C361" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D361" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -7584,10 +7689,10 @@
         <v>268</v>
       </c>
       <c r="C362" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D362" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -7598,10 +7703,10 @@
         <v>268</v>
       </c>
       <c r="C363" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D363" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -7612,10 +7717,10 @@
         <v>268</v>
       </c>
       <c r="C364" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D364" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -7626,10 +7731,10 @@
         <v>268</v>
       </c>
       <c r="C365" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D365" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -7640,10 +7745,10 @@
         <v>268</v>
       </c>
       <c r="C366" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D366" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -7654,10 +7759,10 @@
         <v>266</v>
       </c>
       <c r="C367" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D367" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -7668,10 +7773,10 @@
         <v>266</v>
       </c>
       <c r="C368" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D368" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -7682,10 +7787,10 @@
         <v>266</v>
       </c>
       <c r="C369" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D369" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -7696,10 +7801,10 @@
         <v>240</v>
       </c>
       <c r="C370" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D370" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -7710,10 +7815,10 @@
         <v>282</v>
       </c>
       <c r="C371" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D371" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -7724,10 +7829,10 @@
         <v>282</v>
       </c>
       <c r="C372" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D372" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -7738,10 +7843,10 @@
         <v>15</v>
       </c>
       <c r="C373" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D373" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -7752,10 +7857,10 @@
         <v>15</v>
       </c>
       <c r="C374" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D374" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -7766,10 +7871,10 @@
         <v>15</v>
       </c>
       <c r="C375" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D375" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -7780,10 +7885,10 @@
         <v>15</v>
       </c>
       <c r="C376" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D376" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -7794,10 +7899,10 @@
         <v>316</v>
       </c>
       <c r="C377" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D377" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -7808,10 +7913,10 @@
         <v>316</v>
       </c>
       <c r="C378" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D378" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -7822,10 +7927,10 @@
         <v>309</v>
       </c>
       <c r="C379" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D379" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -7836,10 +7941,10 @@
         <v>381</v>
       </c>
       <c r="C380" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D380" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -7850,10 +7955,10 @@
         <v>119</v>
       </c>
       <c r="C381" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D381" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -7864,10 +7969,10 @@
         <v>119</v>
       </c>
       <c r="C382" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D382" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -7878,10 +7983,10 @@
         <v>119</v>
       </c>
       <c r="C383" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D383" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -7892,10 +7997,10 @@
         <v>78</v>
       </c>
       <c r="C384" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D384" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -7906,10 +8011,10 @@
         <v>78</v>
       </c>
       <c r="C385" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D385" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -7920,10 +8025,10 @@
         <v>78</v>
       </c>
       <c r="C386" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D386" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -7934,10 +8039,10 @@
         <v>78</v>
       </c>
       <c r="C387" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D387" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -7948,10 +8053,10 @@
         <v>78</v>
       </c>
       <c r="C388" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D388" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -7962,10 +8067,10 @@
         <v>78</v>
       </c>
       <c r="C389" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D389" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -7976,10 +8081,10 @@
         <v>78</v>
       </c>
       <c r="C390" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D390" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -7990,10 +8095,10 @@
         <v>23</v>
       </c>
       <c r="C391" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D391" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -8004,10 +8109,10 @@
         <v>218</v>
       </c>
       <c r="C392" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D392" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -8018,10 +8123,10 @@
         <v>218</v>
       </c>
       <c r="C393" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D393" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -8032,10 +8137,10 @@
         <v>218</v>
       </c>
       <c r="C394" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D394" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -8046,10 +8151,10 @@
         <v>218</v>
       </c>
       <c r="C395" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D395" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -8060,10 +8165,10 @@
         <v>222</v>
       </c>
       <c r="C396" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D396" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -8074,10 +8179,10 @@
         <v>222</v>
       </c>
       <c r="C397" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D397" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -8088,10 +8193,10 @@
         <v>222</v>
       </c>
       <c r="C398" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D398" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -8102,10 +8207,10 @@
         <v>222</v>
       </c>
       <c r="C399" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D399" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -8116,10 +8221,10 @@
         <v>401</v>
       </c>
       <c r="C400" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D400" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -8130,10 +8235,10 @@
         <v>402</v>
       </c>
       <c r="C401" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D401" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -8144,10 +8249,10 @@
         <v>403</v>
       </c>
       <c r="C402" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D402" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -8158,10 +8263,10 @@
         <v>404</v>
       </c>
       <c r="C403" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D403" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -8172,10 +8277,10 @@
         <v>405</v>
       </c>
       <c r="C404" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D404" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -8186,10 +8291,10 @@
         <v>406</v>
       </c>
       <c r="C405" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D405" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -8200,10 +8305,10 @@
         <v>407</v>
       </c>
       <c r="C406" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D406" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -8214,10 +8319,10 @@
         <v>408</v>
       </c>
       <c r="C407" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D407" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -8228,10 +8333,10 @@
         <v>409</v>
       </c>
       <c r="C408" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D408" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -8242,10 +8347,10 @@
         <v>410</v>
       </c>
       <c r="C409" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D409" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -8256,10 +8361,10 @@
         <v>565</v>
       </c>
       <c r="C410" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D410" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -8270,10 +8375,10 @@
         <v>412</v>
       </c>
       <c r="C411" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D411" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -8284,10 +8389,10 @@
         <v>413</v>
       </c>
       <c r="C412" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D412" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -8298,10 +8403,10 @@
         <v>312</v>
       </c>
       <c r="C413" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D413" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -8312,10 +8417,10 @@
         <v>415</v>
       </c>
       <c r="C414" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D414" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -8326,10 +8431,10 @@
         <v>416</v>
       </c>
       <c r="C415" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D415" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -8340,10 +8445,10 @@
         <v>417</v>
       </c>
       <c r="C416" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D416" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -8354,10 +8459,10 @@
         <v>418</v>
       </c>
       <c r="C417" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D417" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -8368,10 +8473,10 @@
         <v>419</v>
       </c>
       <c r="C418" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D418" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -8382,10 +8487,10 @@
         <v>420</v>
       </c>
       <c r="C419" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D419" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -8396,10 +8501,10 @@
         <v>421</v>
       </c>
       <c r="C420" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D420" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -8410,10 +8515,10 @@
         <v>422</v>
       </c>
       <c r="C421" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D421" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -8424,10 +8529,10 @@
         <v>423</v>
       </c>
       <c r="C422" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D422" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -8438,10 +8543,10 @@
         <v>424</v>
       </c>
       <c r="C423" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D423" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -8452,10 +8557,10 @@
         <v>425</v>
       </c>
       <c r="C424" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D424" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -8466,10 +8571,10 @@
         <v>426</v>
       </c>
       <c r="C425" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D425" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -8480,10 +8585,10 @@
         <v>427</v>
       </c>
       <c r="C426" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D426" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -8494,10 +8599,10 @@
         <v>428</v>
       </c>
       <c r="C427" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D427" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -8508,10 +8613,10 @@
         <v>429</v>
       </c>
       <c r="C428" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D428" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -8522,10 +8627,10 @@
         <v>430</v>
       </c>
       <c r="C429" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D429" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -8536,10 +8641,10 @@
         <v>431</v>
       </c>
       <c r="C430" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D430" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -8550,10 +8655,10 @@
         <v>432</v>
       </c>
       <c r="C431" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D431" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -8564,10 +8669,10 @@
         <v>433</v>
       </c>
       <c r="C432" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D432" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -8578,10 +8683,10 @@
         <v>434</v>
       </c>
       <c r="C433" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D433" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -8592,10 +8697,10 @@
         <v>435</v>
       </c>
       <c r="C434" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D434" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -8606,10 +8711,10 @@
         <v>436</v>
       </c>
       <c r="C435" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D435" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -8620,10 +8725,10 @@
         <v>437</v>
       </c>
       <c r="C436" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D436" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -8634,10 +8739,10 @@
         <v>438</v>
       </c>
       <c r="C437" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D437" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -8648,10 +8753,10 @@
         <v>439</v>
       </c>
       <c r="C438" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D438" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -8662,10 +8767,10 @@
         <v>440</v>
       </c>
       <c r="C439" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D439" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -8676,10 +8781,10 @@
         <v>441</v>
       </c>
       <c r="C440" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D440" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -8690,10 +8795,10 @@
         <v>442</v>
       </c>
       <c r="C441" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D441" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -8704,10 +8809,10 @@
         <v>443</v>
       </c>
       <c r="C442" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D442" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -8718,10 +8823,10 @@
         <v>444</v>
       </c>
       <c r="C443" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D443" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -8732,10 +8837,10 @@
         <v>445</v>
       </c>
       <c r="C444" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D444" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -8746,10 +8851,10 @@
         <v>446</v>
       </c>
       <c r="C445" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D445" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -8760,10 +8865,10 @@
         <v>447</v>
       </c>
       <c r="C446" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D446" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -8774,10 +8879,10 @@
         <v>448</v>
       </c>
       <c r="C447" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D447" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -8788,10 +8893,10 @@
         <v>449</v>
       </c>
       <c r="C448" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D448" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -8802,10 +8907,10 @@
         <v>450</v>
       </c>
       <c r="C449" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D449" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -8816,10 +8921,10 @@
         <v>451</v>
       </c>
       <c r="C450" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D450" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -8830,10 +8935,10 @@
         <v>452</v>
       </c>
       <c r="C451" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D451" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -8844,10 +8949,10 @@
         <v>453</v>
       </c>
       <c r="C452" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D452" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -8858,10 +8963,10 @@
         <v>454</v>
       </c>
       <c r="C453" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D453" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -8872,10 +8977,10 @@
         <v>455</v>
       </c>
       <c r="C454" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D454" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -8886,10 +8991,10 @@
         <v>456</v>
       </c>
       <c r="C455" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D455" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -8900,10 +9005,10 @@
         <v>457</v>
       </c>
       <c r="C456" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D456" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -8914,10 +9019,10 @@
         <v>458</v>
       </c>
       <c r="C457" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D457" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -8928,10 +9033,10 @@
         <v>459</v>
       </c>
       <c r="C458" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D458" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -8942,10 +9047,10 @@
         <v>460</v>
       </c>
       <c r="C459" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D459" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -8956,10 +9061,10 @@
         <v>461</v>
       </c>
       <c r="C460" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D460" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -8970,10 +9075,10 @@
         <v>462</v>
       </c>
       <c r="C461" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D461" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -8984,10 +9089,10 @@
         <v>463</v>
       </c>
       <c r="C462" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D462" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -8998,10 +9103,10 @@
         <v>464</v>
       </c>
       <c r="C463" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D463" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -9012,10 +9117,10 @@
         <v>465</v>
       </c>
       <c r="C464" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D464" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -9026,10 +9131,10 @@
         <v>466</v>
       </c>
       <c r="C465" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D465" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -9040,10 +9145,10 @@
         <v>467</v>
       </c>
       <c r="C466" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D466" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -9054,10 +9159,10 @@
         <v>468</v>
       </c>
       <c r="C467" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D467" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -9068,10 +9173,10 @@
         <v>469</v>
       </c>
       <c r="C468" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D468" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -9082,10 +9187,10 @@
         <v>470</v>
       </c>
       <c r="C469" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D469" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -9096,10 +9201,10 @@
         <v>471</v>
       </c>
       <c r="C470" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D470" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -9110,10 +9215,10 @@
         <v>472</v>
       </c>
       <c r="C471" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D471" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -9124,10 +9229,10 @@
         <v>473</v>
       </c>
       <c r="C472" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D472" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -9138,10 +9243,10 @@
         <v>474</v>
       </c>
       <c r="C473" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D473" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -9152,10 +9257,10 @@
         <v>475</v>
       </c>
       <c r="C474" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D474" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -9166,10 +9271,10 @@
         <v>476</v>
       </c>
       <c r="C475" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D475" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -9180,10 +9285,10 @@
         <v>477</v>
       </c>
       <c r="C476" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D476" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -9194,10 +9299,10 @@
         <v>478</v>
       </c>
       <c r="C477" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D477" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -9208,10 +9313,10 @@
         <v>479</v>
       </c>
       <c r="C478" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D478" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -9222,10 +9327,10 @@
         <v>480</v>
       </c>
       <c r="C479" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D479" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -9236,10 +9341,10 @@
         <v>481</v>
       </c>
       <c r="C480" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D480" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -9250,10 +9355,10 @@
         <v>482</v>
       </c>
       <c r="C481" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D481" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -9264,10 +9369,10 @@
         <v>483</v>
       </c>
       <c r="C482" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D482" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -9278,10 +9383,10 @@
         <v>484</v>
       </c>
       <c r="C483" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D483" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -9292,10 +9397,10 @@
         <v>485</v>
       </c>
       <c r="C484" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D484" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -9306,10 +9411,10 @@
         <v>486</v>
       </c>
       <c r="C485" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D485" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -9320,10 +9425,10 @@
         <v>487</v>
       </c>
       <c r="C486" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D486" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -9334,10 +9439,10 @@
         <v>488</v>
       </c>
       <c r="C487" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D487" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -9348,10 +9453,10 @@
         <v>489</v>
       </c>
       <c r="C488" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D488" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -9362,10 +9467,10 @@
         <v>490</v>
       </c>
       <c r="C489" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D489" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -9376,10 +9481,10 @@
         <v>491</v>
       </c>
       <c r="C490" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D490" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -9390,10 +9495,10 @@
         <v>492</v>
       </c>
       <c r="C491" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D491" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -9404,10 +9509,10 @@
         <v>493</v>
       </c>
       <c r="C492" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D492" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -9418,10 +9523,10 @@
         <v>494</v>
       </c>
       <c r="C493" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D493" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -9432,10 +9537,10 @@
         <v>495</v>
       </c>
       <c r="C494" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D494" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -9446,10 +9551,10 @@
         <v>496</v>
       </c>
       <c r="C495" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D495" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -9460,10 +9565,10 @@
         <v>497</v>
       </c>
       <c r="C496" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D496" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -9474,10 +9579,10 @@
         <v>498</v>
       </c>
       <c r="C497" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D497" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -9488,10 +9593,10 @@
         <v>499</v>
       </c>
       <c r="C498" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D498" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -9502,10 +9607,10 @@
         <v>500</v>
       </c>
       <c r="C499" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D499" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -9516,10 +9621,10 @@
         <v>501</v>
       </c>
       <c r="C500" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D500" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -9530,10 +9635,10 @@
         <v>502</v>
       </c>
       <c r="C501" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D501" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -9544,10 +9649,10 @@
         <v>503</v>
       </c>
       <c r="C502" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D502" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -9558,10 +9663,10 @@
         <v>504</v>
       </c>
       <c r="C503" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D503" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -9572,10 +9677,10 @@
         <v>505</v>
       </c>
       <c r="C504" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D504" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -9586,10 +9691,10 @@
         <v>506</v>
       </c>
       <c r="C505" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D505" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -9600,10 +9705,10 @@
         <v>507</v>
       </c>
       <c r="C506" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D506" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -9614,10 +9719,10 @@
         <v>508</v>
       </c>
       <c r="C507" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D507" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -9628,10 +9733,10 @@
         <v>509</v>
       </c>
       <c r="C508" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D508" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -9642,10 +9747,10 @@
         <v>510</v>
       </c>
       <c r="C509" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D509" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -9656,10 +9761,10 @@
         <v>511</v>
       </c>
       <c r="C510" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D510" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -9670,10 +9775,10 @@
         <v>512</v>
       </c>
       <c r="C511" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D511" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -9684,10 +9789,10 @@
         <v>513</v>
       </c>
       <c r="C512" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D512" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -9698,10 +9803,10 @@
         <v>514</v>
       </c>
       <c r="C513" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D513" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -9712,10 +9817,10 @@
         <v>515</v>
       </c>
       <c r="C514" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D514" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -9726,10 +9831,10 @@
         <v>516</v>
       </c>
       <c r="C515" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D515" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -9740,10 +9845,10 @@
         <v>517</v>
       </c>
       <c r="C516" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D516" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -9754,10 +9859,10 @@
         <v>518</v>
       </c>
       <c r="C517" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D517" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -9768,10 +9873,10 @@
         <v>519</v>
       </c>
       <c r="C518" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="D518" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -9782,10 +9887,10 @@
         <v>243</v>
       </c>
       <c r="C519" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D519" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -9796,10 +9901,10 @@
         <v>243</v>
       </c>
       <c r="C520" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D520" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -9810,10 +9915,10 @@
         <v>243</v>
       </c>
       <c r="C521" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D521" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -9824,10 +9929,10 @@
         <v>49</v>
       </c>
       <c r="C522" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D522" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -9835,13 +9940,13 @@
         <v>524</v>
       </c>
       <c r="B523" t="s">
-        <v>663</v>
+        <v>695</v>
       </c>
       <c r="C523" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D523" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -9849,13 +9954,13 @@
         <v>525</v>
       </c>
       <c r="B524" t="s">
-        <v>663</v>
+        <v>695</v>
       </c>
       <c r="C524" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D524" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -9863,13 +9968,13 @@
         <v>526</v>
       </c>
       <c r="B525" t="s">
-        <v>664</v>
+        <v>696</v>
       </c>
       <c r="C525" t="s">
-        <v>707</v>
+        <v>742</v>
       </c>
       <c r="D525" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -9880,10 +9985,10 @@
         <v>545</v>
       </c>
       <c r="C526" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D526" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -9894,10 +9999,10 @@
         <v>546</v>
       </c>
       <c r="C527" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D527" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -9908,10 +10013,10 @@
         <v>548</v>
       </c>
       <c r="C528" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D528" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -9922,10 +10027,10 @@
         <v>564</v>
       </c>
       <c r="C529" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D529" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -9936,10 +10041,10 @@
         <v>558</v>
       </c>
       <c r="C530" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D530" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -9950,10 +10055,10 @@
         <v>556</v>
       </c>
       <c r="C531" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D531" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -9964,10 +10069,10 @@
         <v>555</v>
       </c>
       <c r="C532" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D532" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -9975,13 +10080,13 @@
         <v>534</v>
       </c>
       <c r="B533" t="s">
-        <v>665</v>
+        <v>697</v>
       </c>
       <c r="C533" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D533" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -9992,10 +10097,10 @@
         <v>566</v>
       </c>
       <c r="C534" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D534" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -10006,10 +10111,10 @@
         <v>554</v>
       </c>
       <c r="C535" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D535" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -10020,10 +10125,10 @@
         <v>554</v>
       </c>
       <c r="C536" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D536" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -10034,10 +10139,10 @@
         <v>568</v>
       </c>
       <c r="C537" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D537" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -10048,10 +10153,10 @@
         <v>569</v>
       </c>
       <c r="C538" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D538" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -10062,10 +10167,10 @@
         <v>570</v>
       </c>
       <c r="C539" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D539" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -10076,10 +10181,10 @@
         <v>571</v>
       </c>
       <c r="C540" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D540" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -10090,10 +10195,10 @@
         <v>572</v>
       </c>
       <c r="C541" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D541" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -10104,10 +10209,10 @@
         <v>573</v>
       </c>
       <c r="C542" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D542" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -10118,10 +10223,10 @@
         <v>574</v>
       </c>
       <c r="C543" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D543" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -10132,10 +10237,10 @@
         <v>545</v>
       </c>
       <c r="C544" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D544" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -10146,10 +10251,10 @@
         <v>546</v>
       </c>
       <c r="C545" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D545" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -10160,10 +10265,10 @@
         <v>547</v>
       </c>
       <c r="C546" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D546" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -10174,10 +10279,10 @@
         <v>548</v>
       </c>
       <c r="C547" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D547" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -10188,10 +10293,10 @@
         <v>549</v>
       </c>
       <c r="C548" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D548" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -10202,10 +10307,10 @@
         <v>550</v>
       </c>
       <c r="C549" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D549" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -10216,10 +10321,10 @@
         <v>551</v>
       </c>
       <c r="C550" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D550" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -10230,10 +10335,10 @@
         <v>552</v>
       </c>
       <c r="C551" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D551" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -10244,10 +10349,10 @@
         <v>553</v>
       </c>
       <c r="C552" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D552" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -10258,10 +10363,10 @@
         <v>554</v>
       </c>
       <c r="C553" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D553" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -10272,10 +10377,10 @@
         <v>555</v>
       </c>
       <c r="C554" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D554" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -10286,10 +10391,10 @@
         <v>556</v>
       </c>
       <c r="C555" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D555" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -10300,10 +10405,10 @@
         <v>557</v>
       </c>
       <c r="C556" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D556" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -10314,10 +10419,10 @@
         <v>558</v>
       </c>
       <c r="C557" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D557" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -10328,10 +10433,10 @@
         <v>559</v>
       </c>
       <c r="C558" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D558" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -10342,10 +10447,10 @@
         <v>560</v>
       </c>
       <c r="C559" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D559" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -10356,10 +10461,10 @@
         <v>561</v>
       </c>
       <c r="C560" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D560" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="561" spans="1:4">
@@ -10370,10 +10475,10 @@
         <v>562</v>
       </c>
       <c r="C561" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D561" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="562" spans="1:4">
@@ -10384,10 +10489,10 @@
         <v>563</v>
       </c>
       <c r="C562" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D562" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -10398,10 +10503,10 @@
         <v>564</v>
       </c>
       <c r="C563" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D563" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -10412,10 +10517,10 @@
         <v>565</v>
       </c>
       <c r="C564" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D564" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="565" spans="1:4">
@@ -10426,10 +10531,10 @@
         <v>566</v>
       </c>
       <c r="C565" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D565" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -10440,10 +10545,10 @@
         <v>567</v>
       </c>
       <c r="C566" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D566" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -10454,10 +10559,10 @@
         <v>568</v>
       </c>
       <c r="C567" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D567" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -10468,10 +10573,10 @@
         <v>569</v>
       </c>
       <c r="C568" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D568" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -10482,10 +10587,10 @@
         <v>570</v>
       </c>
       <c r="C569" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D569" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -10496,10 +10601,10 @@
         <v>571</v>
       </c>
       <c r="C570" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D570" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -10510,10 +10615,10 @@
         <v>572</v>
       </c>
       <c r="C571" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D571" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -10524,10 +10629,10 @@
         <v>573</v>
       </c>
       <c r="C572" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D572" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -10538,10 +10643,10 @@
         <v>574</v>
       </c>
       <c r="C573" t="s">
-        <v>710</v>
+        <v>745</v>
       </c>
       <c r="D573" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -10552,10 +10657,10 @@
         <v>228</v>
       </c>
       <c r="C574" t="s">
-        <v>711</v>
+        <v>746</v>
       </c>
       <c r="D574" t="s">
-        <v>715</v>
+        <v>750</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -10566,10 +10671,10 @@
         <v>78</v>
       </c>
       <c r="C575" t="s">
-        <v>711</v>
+        <v>746</v>
       </c>
       <c r="D575" t="s">
-        <v>715</v>
+        <v>750</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -10577,13 +10682,13 @@
         <v>577</v>
       </c>
       <c r="B576" t="s">
-        <v>666</v>
+        <v>698</v>
       </c>
       <c r="C576" t="s">
-        <v>712</v>
+        <v>747</v>
       </c>
       <c r="D576" t="s">
-        <v>715</v>
+        <v>750</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -10591,13 +10696,13 @@
         <v>578</v>
       </c>
       <c r="B577" t="s">
-        <v>667</v>
+        <v>699</v>
       </c>
       <c r="C577" t="s">
-        <v>712</v>
+        <v>747</v>
       </c>
       <c r="D577" t="s">
-        <v>715</v>
+        <v>750</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -10608,10 +10713,10 @@
         <v>579</v>
       </c>
       <c r="C578" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="D578" t="s">
-        <v>714</v>
+        <v>749</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -10622,7 +10727,7 @@
         <v>57</v>
       </c>
       <c r="C579" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="580" spans="1:4">
@@ -10633,7 +10738,7 @@
         <v>208</v>
       </c>
       <c r="C580" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -10641,10 +10746,10 @@
         <v>582</v>
       </c>
       <c r="B581" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="C581" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="582" spans="1:4">
@@ -10652,10 +10757,10 @@
         <v>583</v>
       </c>
       <c r="B582" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="C582" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="583" spans="1:4">
@@ -10663,10 +10768,10 @@
         <v>584</v>
       </c>
       <c r="B583" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="C583" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="584" spans="1:4">
@@ -10677,7 +10782,7 @@
         <v>119</v>
       </c>
       <c r="C584" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="585" spans="1:4">
@@ -10685,10 +10790,10 @@
         <v>586</v>
       </c>
       <c r="B585" t="s">
-        <v>669</v>
+        <v>700</v>
       </c>
       <c r="C585" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -10696,10 +10801,10 @@
         <v>587</v>
       </c>
       <c r="B586" t="s">
-        <v>670</v>
+        <v>701</v>
       </c>
       <c r="C586" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="587" spans="1:4">
@@ -10710,7 +10815,7 @@
         <v>107</v>
       </c>
       <c r="C587" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="588" spans="1:4">
@@ -10718,10 +10823,10 @@
         <v>589</v>
       </c>
       <c r="B588" t="s">
-        <v>671</v>
+        <v>702</v>
       </c>
       <c r="C588" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="589" spans="1:4">
@@ -10732,7 +10837,7 @@
         <v>591</v>
       </c>
       <c r="C589" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="590" spans="1:4">
@@ -10743,7 +10848,7 @@
         <v>591</v>
       </c>
       <c r="C590" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -10751,10 +10856,10 @@
         <v>592</v>
       </c>
       <c r="B591" t="s">
-        <v>672</v>
+        <v>703</v>
       </c>
       <c r="C591" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="592" spans="1:4">
@@ -10765,7 +10870,7 @@
         <v>182</v>
       </c>
       <c r="C592" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="593" spans="1:3">
@@ -10773,10 +10878,10 @@
         <v>594</v>
       </c>
       <c r="B593" t="s">
-        <v>673</v>
+        <v>704</v>
       </c>
       <c r="C593" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="594" spans="1:3">
@@ -10784,10 +10889,10 @@
         <v>595</v>
       </c>
       <c r="B594" t="s">
-        <v>674</v>
+        <v>705</v>
       </c>
       <c r="C594" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="595" spans="1:3">
@@ -10795,10 +10900,10 @@
         <v>596</v>
       </c>
       <c r="B595" t="s">
-        <v>675</v>
+        <v>706</v>
       </c>
       <c r="C595" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="596" spans="1:3">
@@ -10806,10 +10911,10 @@
         <v>597</v>
       </c>
       <c r="B596" t="s">
-        <v>675</v>
+        <v>706</v>
       </c>
       <c r="C596" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="597" spans="1:3">
@@ -10817,10 +10922,10 @@
         <v>598</v>
       </c>
       <c r="B597" t="s">
-        <v>676</v>
+        <v>707</v>
       </c>
       <c r="C597" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="598" spans="1:3">
@@ -10828,10 +10933,10 @@
         <v>599</v>
       </c>
       <c r="B598" t="s">
-        <v>677</v>
+        <v>708</v>
       </c>
       <c r="C598" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="599" spans="1:3">
@@ -10839,10 +10944,10 @@
         <v>600</v>
       </c>
       <c r="B599" t="s">
-        <v>678</v>
+        <v>709</v>
       </c>
       <c r="C599" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="600" spans="1:3">
@@ -10850,10 +10955,10 @@
         <v>601</v>
       </c>
       <c r="B600" t="s">
-        <v>679</v>
+        <v>710</v>
       </c>
       <c r="C600" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="601" spans="1:3">
@@ -10861,10 +10966,10 @@
         <v>602</v>
       </c>
       <c r="B601" t="s">
-        <v>680</v>
+        <v>711</v>
       </c>
       <c r="C601" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="602" spans="1:3">
@@ -10872,10 +10977,10 @@
         <v>603</v>
       </c>
       <c r="B602" t="s">
-        <v>681</v>
+        <v>712</v>
       </c>
       <c r="C602" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="603" spans="1:3">
@@ -10883,10 +10988,10 @@
         <v>604</v>
       </c>
       <c r="B603" t="s">
-        <v>682</v>
+        <v>713</v>
       </c>
       <c r="C603" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="604" spans="1:3">
@@ -10894,10 +10999,10 @@
         <v>605</v>
       </c>
       <c r="B604" t="s">
-        <v>683</v>
+        <v>714</v>
       </c>
       <c r="C604" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="605" spans="1:3">
@@ -10905,10 +11010,10 @@
         <v>606</v>
       </c>
       <c r="B605" t="s">
-        <v>684</v>
+        <v>715</v>
       </c>
       <c r="C605" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="606" spans="1:3">
@@ -10916,10 +11021,10 @@
         <v>607</v>
       </c>
       <c r="B606" t="s">
-        <v>685</v>
+        <v>716</v>
       </c>
       <c r="C606" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="607" spans="1:3">
@@ -10930,7 +11035,7 @@
         <v>450</v>
       </c>
       <c r="C607" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="608" spans="1:3">
@@ -10941,7 +11046,7 @@
         <v>314</v>
       </c>
       <c r="C608" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="609" spans="1:3">
@@ -10949,10 +11054,10 @@
         <v>610</v>
       </c>
       <c r="B609" t="s">
-        <v>686</v>
+        <v>717</v>
       </c>
       <c r="C609" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="610" spans="1:3">
@@ -10960,10 +11065,10 @@
         <v>611</v>
       </c>
       <c r="B610" t="s">
-        <v>687</v>
+        <v>718</v>
       </c>
       <c r="C610" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="611" spans="1:3">
@@ -10971,10 +11076,10 @@
         <v>612</v>
       </c>
       <c r="B611" t="s">
-        <v>688</v>
+        <v>719</v>
       </c>
       <c r="C611" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="612" spans="1:3">
@@ -10982,10 +11087,10 @@
         <v>613</v>
       </c>
       <c r="B612" t="s">
-        <v>689</v>
+        <v>720</v>
       </c>
       <c r="C612" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="613" spans="1:3">
@@ -10993,10 +11098,10 @@
         <v>614</v>
       </c>
       <c r="B613" t="s">
-        <v>690</v>
+        <v>721</v>
       </c>
       <c r="C613" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="614" spans="1:3">
@@ -11004,10 +11109,10 @@
         <v>615</v>
       </c>
       <c r="B614" t="s">
-        <v>691</v>
+        <v>722</v>
       </c>
       <c r="C614" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="615" spans="1:3">
@@ -11018,7 +11123,7 @@
         <v>91</v>
       </c>
       <c r="C615" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="616" spans="1:3">
@@ -11026,10 +11131,10 @@
         <v>617</v>
       </c>
       <c r="B616" t="s">
-        <v>679</v>
+        <v>710</v>
       </c>
       <c r="C616" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="617" spans="1:3">
@@ -11037,10 +11142,10 @@
         <v>618</v>
       </c>
       <c r="B617" t="s">
-        <v>692</v>
+        <v>723</v>
       </c>
       <c r="C617" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="618" spans="1:3">
@@ -11048,10 +11153,10 @@
         <v>619</v>
       </c>
       <c r="B618" t="s">
-        <v>693</v>
+        <v>724</v>
       </c>
       <c r="C618" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="619" spans="1:3">
@@ -11059,10 +11164,10 @@
         <v>620</v>
       </c>
       <c r="B619" t="s">
-        <v>694</v>
+        <v>725</v>
       </c>
       <c r="C619" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="620" spans="1:3">
@@ -11073,7 +11178,7 @@
         <v>219</v>
       </c>
       <c r="C620" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="621" spans="1:3">
@@ -11084,7 +11189,7 @@
         <v>219</v>
       </c>
       <c r="C621" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="622" spans="1:3">
@@ -11095,7 +11200,7 @@
         <v>219</v>
       </c>
       <c r="C622" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="623" spans="1:3">
@@ -11106,7 +11211,7 @@
         <v>219</v>
       </c>
       <c r="C623" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="624" spans="1:3">
@@ -11117,7 +11222,7 @@
         <v>219</v>
       </c>
       <c r="C624" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="625" spans="1:3">
@@ -11128,7 +11233,7 @@
         <v>626</v>
       </c>
       <c r="C625" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="626" spans="1:3">
@@ -11136,10 +11241,10 @@
         <v>627</v>
       </c>
       <c r="B626" t="s">
-        <v>695</v>
+        <v>726</v>
       </c>
       <c r="C626" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="627" spans="1:3">
@@ -11147,10 +11252,10 @@
         <v>628</v>
       </c>
       <c r="B627" t="s">
-        <v>696</v>
+        <v>727</v>
       </c>
       <c r="C627" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="628" spans="1:3">
@@ -11161,7 +11266,7 @@
         <v>184</v>
       </c>
       <c r="C628" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="629" spans="1:3">
@@ -11172,7 +11277,7 @@
         <v>178</v>
       </c>
       <c r="C629" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="630" spans="1:3">
@@ -11180,10 +11285,10 @@
         <v>631</v>
       </c>
       <c r="B630" t="s">
-        <v>697</v>
+        <v>728</v>
       </c>
       <c r="C630" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="631" spans="1:3">
@@ -11191,10 +11296,10 @@
         <v>632</v>
       </c>
       <c r="B631" t="s">
-        <v>698</v>
+        <v>729</v>
       </c>
       <c r="C631" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="632" spans="1:3">
@@ -11202,10 +11307,10 @@
         <v>633</v>
       </c>
       <c r="B632" t="s">
-        <v>699</v>
+        <v>730</v>
       </c>
       <c r="C632" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="633" spans="1:3">
@@ -11213,10 +11318,10 @@
         <v>634</v>
       </c>
       <c r="B633" t="s">
-        <v>700</v>
+        <v>731</v>
       </c>
       <c r="C633" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="634" spans="1:3">
@@ -11224,10 +11329,10 @@
         <v>635</v>
       </c>
       <c r="B634" t="s">
-        <v>688</v>
+        <v>719</v>
       </c>
       <c r="C634" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="635" spans="1:3">
@@ -11238,7 +11343,7 @@
         <v>636</v>
       </c>
       <c r="C635" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="636" spans="1:3">
@@ -11249,7 +11354,7 @@
         <v>637</v>
       </c>
       <c r="C636" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="637" spans="1:3">
@@ -11257,10 +11362,10 @@
         <v>638</v>
       </c>
       <c r="B637" t="s">
-        <v>701</v>
+        <v>732</v>
       </c>
       <c r="C637" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="638" spans="1:3">
@@ -11268,10 +11373,10 @@
         <v>639</v>
       </c>
       <c r="B638" t="s">
-        <v>702</v>
+        <v>733</v>
       </c>
       <c r="C638" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="639" spans="1:3">
@@ -11279,10 +11384,10 @@
         <v>640</v>
       </c>
       <c r="B639" t="s">
-        <v>703</v>
+        <v>734</v>
       </c>
       <c r="C639" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="640" spans="1:3">
@@ -11290,10 +11395,10 @@
         <v>641</v>
       </c>
       <c r="B640" t="s">
-        <v>704</v>
+        <v>735</v>
       </c>
       <c r="C640" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="641" spans="1:3">
@@ -11301,10 +11406,10 @@
         <v>642</v>
       </c>
       <c r="B641" t="s">
-        <v>705</v>
+        <v>736</v>
       </c>
       <c r="C641" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="642" spans="1:3">
@@ -11312,10 +11417,10 @@
         <v>643</v>
       </c>
       <c r="B642" t="s">
-        <v>706</v>
+        <v>737</v>
       </c>
       <c r="C642" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="643" spans="1:3">
@@ -11326,7 +11431,7 @@
         <v>644</v>
       </c>
       <c r="C643" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="644" spans="1:3">
@@ -11337,7 +11442,7 @@
         <v>645</v>
       </c>
       <c r="C644" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="645" spans="1:3">
@@ -11348,7 +11453,7 @@
         <v>646</v>
       </c>
       <c r="C645" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="646" spans="1:3">
@@ -11359,7 +11464,7 @@
         <v>647</v>
       </c>
       <c r="C646" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="647" spans="1:3">
@@ -11370,7 +11475,7 @@
         <v>648</v>
       </c>
       <c r="C647" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="648" spans="1:3">
@@ -11381,7 +11486,7 @@
         <v>649</v>
       </c>
       <c r="C648" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="649" spans="1:3">
@@ -11392,7 +11497,7 @@
         <v>650</v>
       </c>
       <c r="C649" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="650" spans="1:3">
@@ -11403,7 +11508,7 @@
         <v>651</v>
       </c>
       <c r="C650" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="651" spans="1:3">
@@ -11414,7 +11519,7 @@
         <v>652</v>
       </c>
       <c r="C651" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="652" spans="1:3">
@@ -11425,7 +11530,7 @@
         <v>653</v>
       </c>
       <c r="C652" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="653" spans="1:3">
@@ -11436,7 +11541,7 @@
         <v>654</v>
       </c>
       <c r="C653" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="654" spans="1:3">
@@ -11447,7 +11552,7 @@
         <v>655</v>
       </c>
       <c r="C654" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="655" spans="1:3">
@@ -11458,7 +11563,7 @@
         <v>656</v>
       </c>
       <c r="C655" t="s">
-        <v>713</v>
+        <v>748</v>
       </c>
     </row>
     <row r="656" spans="1:3">
@@ -11469,7 +11574,359 @@
         <v>657</v>
       </c>
       <c r="C656" t="s">
-        <v>713</v>
+        <v>748</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3">
+      <c r="A657" t="s">
+        <v>658</v>
+      </c>
+      <c r="B657" t="s">
+        <v>738</v>
+      </c>
+      <c r="C657" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3">
+      <c r="A658" t="s">
+        <v>659</v>
+      </c>
+      <c r="B658" t="s">
+        <v>659</v>
+      </c>
+      <c r="C658" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3">
+      <c r="A659" t="s">
+        <v>660</v>
+      </c>
+      <c r="B659" t="s">
+        <v>660</v>
+      </c>
+      <c r="C659" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="660" spans="1:3">
+      <c r="A660" t="s">
+        <v>661</v>
+      </c>
+      <c r="B660" t="s">
+        <v>661</v>
+      </c>
+      <c r="C660" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="661" spans="1:3">
+      <c r="A661" t="s">
+        <v>662</v>
+      </c>
+      <c r="B661" t="s">
+        <v>662</v>
+      </c>
+      <c r="C661" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3">
+      <c r="A662" t="s">
+        <v>663</v>
+      </c>
+      <c r="B662" t="s">
+        <v>663</v>
+      </c>
+      <c r="C662" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3">
+      <c r="A663" t="s">
+        <v>664</v>
+      </c>
+      <c r="B663" t="s">
+        <v>739</v>
+      </c>
+      <c r="C663" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="664" spans="1:3">
+      <c r="A664" t="s">
+        <v>665</v>
+      </c>
+      <c r="B664" t="s">
+        <v>740</v>
+      </c>
+      <c r="C664" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3">
+      <c r="A665" t="s">
+        <v>666</v>
+      </c>
+      <c r="B665" t="s">
+        <v>666</v>
+      </c>
+      <c r="C665" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3">
+      <c r="A666" t="s">
+        <v>667</v>
+      </c>
+      <c r="B666" t="s">
+        <v>667</v>
+      </c>
+      <c r="C666" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3">
+      <c r="A667" t="s">
+        <v>668</v>
+      </c>
+      <c r="B667" t="s">
+        <v>668</v>
+      </c>
+      <c r="C667" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3">
+      <c r="A668" t="s">
+        <v>669</v>
+      </c>
+      <c r="B668" t="s">
+        <v>741</v>
+      </c>
+      <c r="C668" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="669" spans="1:3">
+      <c r="A669" t="s">
+        <v>670</v>
+      </c>
+      <c r="B669" t="s">
+        <v>670</v>
+      </c>
+      <c r="C669" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3">
+      <c r="A670" t="s">
+        <v>671</v>
+      </c>
+      <c r="B670" t="s">
+        <v>671</v>
+      </c>
+      <c r="C670" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="671" spans="1:3">
+      <c r="A671" t="s">
+        <v>672</v>
+      </c>
+      <c r="B671" t="s">
+        <v>672</v>
+      </c>
+      <c r="C671" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="672" spans="1:3">
+      <c r="A672" t="s">
+        <v>673</v>
+      </c>
+      <c r="B672" t="s">
+        <v>673</v>
+      </c>
+      <c r="C672" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="673" spans="1:3">
+      <c r="A673" t="s">
+        <v>674</v>
+      </c>
+      <c r="B673" t="s">
+        <v>674</v>
+      </c>
+      <c r="C673" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3">
+      <c r="A674" t="s">
+        <v>675</v>
+      </c>
+      <c r="B674" t="s">
+        <v>675</v>
+      </c>
+      <c r="C674" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="675" spans="1:3">
+      <c r="A675" t="s">
+        <v>676</v>
+      </c>
+      <c r="B675" t="s">
+        <v>676</v>
+      </c>
+      <c r="C675" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="676" spans="1:3">
+      <c r="A676" t="s">
+        <v>677</v>
+      </c>
+      <c r="B676" t="s">
+        <v>677</v>
+      </c>
+      <c r="C676" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="677" spans="1:3">
+      <c r="A677" t="s">
+        <v>678</v>
+      </c>
+      <c r="B677" t="s">
+        <v>678</v>
+      </c>
+      <c r="C677" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="678" spans="1:3">
+      <c r="A678" t="s">
+        <v>679</v>
+      </c>
+      <c r="B678" t="s">
+        <v>679</v>
+      </c>
+      <c r="C678" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="679" spans="1:3">
+      <c r="A679" t="s">
+        <v>680</v>
+      </c>
+      <c r="B679" t="s">
+        <v>680</v>
+      </c>
+      <c r="C679" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3">
+      <c r="A680" t="s">
+        <v>681</v>
+      </c>
+      <c r="B680" t="s">
+        <v>681</v>
+      </c>
+      <c r="C680" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="681" spans="1:3">
+      <c r="A681" t="s">
+        <v>682</v>
+      </c>
+      <c r="B681" t="s">
+        <v>682</v>
+      </c>
+      <c r="C681" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3">
+      <c r="A682" t="s">
+        <v>683</v>
+      </c>
+      <c r="B682" t="s">
+        <v>683</v>
+      </c>
+      <c r="C682" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3">
+      <c r="A683" t="s">
+        <v>684</v>
+      </c>
+      <c r="B683" t="s">
+        <v>684</v>
+      </c>
+      <c r="C683" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="684" spans="1:3">
+      <c r="A684" t="s">
+        <v>685</v>
+      </c>
+      <c r="B684" t="s">
+        <v>685</v>
+      </c>
+      <c r="C684" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3">
+      <c r="A685" t="s">
+        <v>686</v>
+      </c>
+      <c r="B685" t="s">
+        <v>686</v>
+      </c>
+      <c r="C685" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3">
+      <c r="A686" t="s">
+        <v>687</v>
+      </c>
+      <c r="B686" t="s">
+        <v>687</v>
+      </c>
+      <c r="C686" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="687" spans="1:3">
+      <c r="A687" t="s">
+        <v>688</v>
+      </c>
+      <c r="B687" t="s">
+        <v>688</v>
+      </c>
+      <c r="C687" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3">
+      <c r="A688" t="s">
+        <v>689</v>
+      </c>
+      <c r="B688" t="s">
+        <v>689</v>
+      </c>
+      <c r="C688" t="s">
+        <v>748</v>
       </c>
     </row>
   </sheetData>

--- a/data/Rename_columns.xlsx
+++ b/data/Rename_columns.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D691"/>
+  <dimension ref="A1:D731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>client_id</t>
+          <t>id_client</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>client_id</t>
+          <t>id_client</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -15076,6 +15076,806 @@
         <is>
           <t>M_PESA</t>
         </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>interest_calculated</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>interet_calcule</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D692" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>encours_credit</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>encours_credit</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D693" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>pret_actif</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>pret_actif</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D694" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>tranche_echeance</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>tranche_echeance</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D695" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>statut_risque</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>statut_risque</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D696" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>par_simplifie_1j</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>par_simplifie_1j</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D697" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>par_simplifie_7j</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>par_simplifie_7j</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D698" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>par_simplifie_30j</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>par_simplifie_30j</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D699" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>date_analyse</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>date_analyse</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D700" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>ecart_encours_sources</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>ecart_encours_sources</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D701" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>encours_sources_incoherents</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>encours_sources_incoherents</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D702" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>savings_account_id_source</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>id_compte_epargne_source</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D703" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>savings_id_correspondant</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>numero_compte_epargne_correspondant</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D704" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>id_compte_turbo_correspondant</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>id_compte_epargne_correspondant</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D705" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>telephone_credit</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>numero_telephone_credit</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D706" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>telephone_epargne</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>numero_telephone_epargne</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D707" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>solde_epargne_courante</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>solde_compte_ouvert</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D708" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>nb_comptes_courants_candidats</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>nombre_comptes_ouverts_candidats</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D709" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>nb_correspondances_identifiant</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>nombre_correspondances_identifiant</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D710" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>methode_rapprochement_epargne</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>methode_rapprochement_epargne</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D711" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>liaison_directe_source</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>liaison_directe_source</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D712" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>correspondance_deduite</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>correspondance_deduite</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D713" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>source_epargne_complete</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>source_epargne_complete</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D714" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>motif_controle</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>motif_controle</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D715" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>statut_controle</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>statut_controle</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D716" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>motifs_controle</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>motifs_controle</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D717" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>statuts_credit</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>statuts_credit</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D718" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>loan_ids</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>ids_credits</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D719" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>nombre_credits</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>nombre_credits</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D720" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>montant_credits</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>montant_credits</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D721" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>montant_rembourse</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>montant_rembourse</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D722" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>encours_sans_echeance</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>encours_sans_echeance</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D723" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>credits_retard_1j</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>credits_retard_1j</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D724" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>credits_retard_30j</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>credits_retard_30j</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D725" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>echeances_renseignees</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>echeances_renseignees</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D726" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>incoherences_encours</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>incoherences_encours</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D727" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>par_1j_pct</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>par_1j_pct</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D728" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>par_7j_pct</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>par_7j_pct</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D729" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>par_30j_pct</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>par_30j_pct</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D730" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>taux_remboursement_pct</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>taux_remboursement_pct</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>M_PESA</t>
+        </is>
+      </c>
+      <c r="D731" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
